--- a/Power_BI/Dashboard_Tabels.xlsx
+++ b/Power_BI/Dashboard_Tabels.xlsx
@@ -1,13 +1,25 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
-<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" mc:Ignorable="x15">
-  <fileVersion appName="xl" lastEdited="6" lowestEdited="6" rupBuild="14420"/>
-  <workbookPr defaultThemeVersion="164011"/>
+<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="6" rupBuild="28526"/>
+  <workbookPr/>
+  <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
+    <mc:Choice Requires="x15">
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="D:\Alight-MEA\Geld-Pilot\Power_BI\"/>
+    </mc:Choice>
+  </mc:AlternateContent>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{CF802C39-DB17-4E37-B119-66D771A5F72B}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="0" yWindow="0" windowWidth="22260" windowHeight="12645"/>
+    <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="12456" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
-    <sheet name="Feuil1" sheetId="1" r:id="rId1"/>
+    <sheet name="Clients" sheetId="1" r:id="rId1"/>
+    <sheet name="Charge-Fix" sheetId="2" r:id="rId2"/>
+    <sheet name="Expense-Results" sheetId="3" r:id="rId3"/>
+    <sheet name="Invoice" sheetId="4" r:id="rId4"/>
+    <sheet name="Revenue-Result" sheetId="5" r:id="rId5"/>
+    <sheet name="Monthly-Activities" sheetId="6" r:id="rId6"/>
+    <sheet name="Annual-Activities" sheetId="7" r:id="rId7"/>
   </sheets>
   <calcPr calcId="162913"/>
   <extLst>
@@ -18,15 +30,602 @@
 </workbook>
 </file>
 
+<file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="331" uniqueCount="192">
+  <si>
+    <t>cr604_client_gpid</t>
+  </si>
+  <si>
+    <t>createdon</t>
+  </si>
+  <si>
+    <t>cr604_cin</t>
+  </si>
+  <si>
+    <t>cr604_name</t>
+  </si>
+  <si>
+    <t>cr604_email</t>
+  </si>
+  <si>
+    <t>cr604_phone</t>
+  </si>
+  <si>
+    <t>cr604_address</t>
+  </si>
+  <si>
+    <t>cr604_clienttype</t>
+  </si>
+  <si>
+    <t>cr604_paymentmethod</t>
+  </si>
+  <si>
+    <t>cr604_currency</t>
+  </si>
+  <si>
+    <t>cr604_status</t>
+  </si>
+  <si>
+    <t>City</t>
+  </si>
+  <si>
+    <t>Country</t>
+  </si>
+  <si>
+    <t>IsActive</t>
+  </si>
+  <si>
+    <t>AC577698-1804-F011-BAE2-002248A332C2</t>
+  </si>
+  <si>
+    <t>18/03/2025 16:46:54</t>
+  </si>
+  <si>
+    <t>wahbi</t>
+  </si>
+  <si>
+    <t>wahbi@gmail.com</t>
+  </si>
+  <si>
+    <t>Ariana_Tunisie</t>
+  </si>
+  <si>
+    <t>Individual</t>
+  </si>
+  <si>
+    <t>Cash</t>
+  </si>
+  <si>
+    <t>Dinar</t>
+  </si>
+  <si>
+    <t>Inactive</t>
+  </si>
+  <si>
+    <t>Ariana</t>
+  </si>
+  <si>
+    <t>Tunisie</t>
+  </si>
+  <si>
+    <t>No</t>
+  </si>
+  <si>
+    <t>0EDA17C5-1804-F011-BAE2-002248A332C2</t>
+  </si>
+  <si>
+    <t>18/03/2025 16:48:09</t>
+  </si>
+  <si>
+    <t>yosri</t>
+  </si>
+  <si>
+    <t>yosri@gmail.com</t>
+  </si>
+  <si>
+    <t>Paris_France</t>
+  </si>
+  <si>
+    <t>Company</t>
+  </si>
+  <si>
+    <t>Bank Transfer</t>
+  </si>
+  <si>
+    <t>Dollar</t>
+  </si>
+  <si>
+    <t>Active</t>
+  </si>
+  <si>
+    <t>Paris</t>
+  </si>
+  <si>
+    <t>France</t>
+  </si>
+  <si>
+    <t>Yes</t>
+  </si>
+  <si>
+    <t>7D6D8841-5304-F011-BAE2-002248A332C2</t>
+  </si>
+  <si>
+    <t>18/03/2025 23:46:49</t>
+  </si>
+  <si>
+    <t>fadi</t>
+  </si>
+  <si>
+    <t>fadi@gmail.com</t>
+  </si>
+  <si>
+    <t>Credit Card</t>
+  </si>
+  <si>
+    <t>Euro</t>
+  </si>
+  <si>
+    <t>C01144C4-9E04-F011-BAE2-002248A332C2</t>
+  </si>
+  <si>
+    <t>19/03/2025 08:47:21</t>
+  </si>
+  <si>
+    <t>syrin</t>
+  </si>
+  <si>
+    <t>syrin@gmail.com</t>
+  </si>
+  <si>
+    <t>Kebili_Tunisie</t>
+  </si>
+  <si>
+    <t>Kebili</t>
+  </si>
+  <si>
+    <t>2A6606CE-AD04-F011-BAE2-002248A332C2</t>
+  </si>
+  <si>
+    <t>19/03/2025 10:35:08</t>
+  </si>
+  <si>
+    <t>Microsoft</t>
+  </si>
+  <si>
+    <t>microsoft@gmail.com</t>
+  </si>
+  <si>
+    <t>Gasrine_Tunisie</t>
+  </si>
+  <si>
+    <t>Gasrine</t>
+  </si>
+  <si>
+    <t>25591607-9205-F011-BAE2-002248A332C2</t>
+  </si>
+  <si>
+    <t>20/03/2025 13:48:40</t>
+  </si>
+  <si>
+    <t>pol</t>
+  </si>
+  <si>
+    <t>pol@gmail.com</t>
+  </si>
+  <si>
+    <t>Expensefix_Id</t>
+  </si>
+  <si>
+    <t>Expense_Name</t>
+  </si>
+  <si>
+    <t>Expense_Type</t>
+  </si>
+  <si>
+    <t>Amount</t>
+  </si>
+  <si>
+    <t>Status</t>
+  </si>
+  <si>
+    <t>25DAC864-1304-F011-BAE2-002248A332C2</t>
+  </si>
+  <si>
+    <t>18/03/2025 16:09:49</t>
+  </si>
+  <si>
+    <t>mee sebela 123</t>
+  </si>
+  <si>
+    <t>Admin</t>
+  </si>
+  <si>
+    <t>Variable</t>
+  </si>
+  <si>
+    <t>8643695F-BE04-F011-BAE2-002248A332C2</t>
+  </si>
+  <si>
+    <t>19/03/2025 12:33:35</t>
+  </si>
+  <si>
+    <t>Expens_A</t>
+  </si>
+  <si>
+    <t>Training</t>
+  </si>
+  <si>
+    <t>Expense_Result_Id</t>
+  </si>
+  <si>
+    <t>Estimated_Amount</t>
+  </si>
+  <si>
+    <t>Actual_Amount</t>
+  </si>
+  <si>
+    <t>Charge_Status</t>
+  </si>
+  <si>
+    <t>Covred_Day</t>
+  </si>
+  <si>
+    <t>Month</t>
+  </si>
+  <si>
+    <t>Year</t>
+  </si>
+  <si>
+    <t>45C173CD-F204-F011-BAE2-002248A332C2</t>
+  </si>
+  <si>
+    <t>19/03/2025 18:49:01</t>
+  </si>
+  <si>
+    <t>Salaire Employé</t>
+  </si>
+  <si>
+    <t>Payroll</t>
+  </si>
+  <si>
+    <t>Charge Normale</t>
+  </si>
+  <si>
+    <t>02</t>
+  </si>
+  <si>
+    <t>12</t>
+  </si>
+  <si>
+    <t>2029</t>
+  </si>
+  <si>
+    <t>46C173CD-F204-F011-BAE2-002248A332C2</t>
+  </si>
+  <si>
+    <t>steg</t>
+  </si>
+  <si>
+    <t>03</t>
+  </si>
+  <si>
+    <t>83529127-F604-F011-BAE2-002248A332C2</t>
+  </si>
+  <si>
+    <t>19/03/2025 19:13:01</t>
+  </si>
+  <si>
+    <t>11</t>
+  </si>
+  <si>
+    <t>2025</t>
+  </si>
+  <si>
+    <t>84529127-F604-F011-BAE2-002248A332C2</t>
+  </si>
+  <si>
+    <t>kree</t>
+  </si>
+  <si>
+    <t>22</t>
+  </si>
+  <si>
+    <t>85529127-F604-F011-BAE2-002248A332C2</t>
+  </si>
+  <si>
+    <t>Surcharge</t>
+  </si>
+  <si>
+    <t>10</t>
+  </si>
+  <si>
+    <t>E017E4CD-BD05-F011-BAE2-002248A332C2</t>
+  </si>
+  <si>
+    <t>20/03/2025 19:02:11</t>
+  </si>
+  <si>
+    <t>01</t>
+  </si>
+  <si>
+    <t>2021</t>
+  </si>
+  <si>
+    <t>E117E4CD-BD05-F011-BAE2-002248A332C2</t>
+  </si>
+  <si>
+    <t>8970B87F-3E89-4471-9163-79FF93845DB7</t>
+  </si>
+  <si>
+    <t>19/03/2025 16:56:17</t>
+  </si>
+  <si>
+    <t>Invoice_Id</t>
+  </si>
+  <si>
+    <t>Client_Name</t>
+  </si>
+  <si>
+    <t>Payed_Amount</t>
+  </si>
+  <si>
+    <t>Peiment_Date</t>
+  </si>
+  <si>
+    <t>Commentaire_Paiement</t>
+  </si>
+  <si>
+    <t>E3C4924E-7C05-F011-BAE2-002248A332C2</t>
+  </si>
+  <si>
+    <t>20/03/2025 11:13:15</t>
+  </si>
+  <si>
+    <t>01/09/2029 00:00:00</t>
+  </si>
+  <si>
+    <t>excellent</t>
+  </si>
+  <si>
+    <t>E4C4924E-7C05-F011-BAE2-002248A332C2</t>
+  </si>
+  <si>
+    <t>05/09/2029 00:00:00</t>
+  </si>
+  <si>
+    <t>E5C4924E-7C05-F011-BAE2-002248A332C2</t>
+  </si>
+  <si>
+    <t>02/09/2029 00:00:00</t>
+  </si>
+  <si>
+    <t>E6C4924E-7C05-F011-BAE2-002248A332C2</t>
+  </si>
+  <si>
+    <t>03/09/2029 00:00:00</t>
+  </si>
+  <si>
+    <t>E9C4924E-7C05-F011-BAE2-002248A332C2</t>
+  </si>
+  <si>
+    <t>20/09/2029 00:00:00</t>
+  </si>
+  <si>
+    <t>4C4E5BC6-8005-F011-BAE2-002248A332C2</t>
+  </si>
+  <si>
+    <t>20/03/2025 11:45:10</t>
+  </si>
+  <si>
+    <t>lamin</t>
+  </si>
+  <si>
+    <t>05/02/2025 01:00:00</t>
+  </si>
+  <si>
+    <t>retard</t>
+  </si>
+  <si>
+    <t>E6BE7FE0-8005-F011-BAE2-002248A332C2</t>
+  </si>
+  <si>
+    <t>20/03/2025 11:45:57</t>
+  </si>
+  <si>
+    <t>salma</t>
+  </si>
+  <si>
+    <t>06/04/2023 01:00:00</t>
+  </si>
+  <si>
+    <t>1F4243E2-BC05-F011-BAE2-002248A332C2</t>
+  </si>
+  <si>
+    <t>20/03/2025 18:55:26</t>
+  </si>
+  <si>
+    <t>02/01/2021 00:00:00</t>
+  </si>
+  <si>
+    <t>204243E2-BC05-F011-BAE2-002248A332C2</t>
+  </si>
+  <si>
+    <t>01/01/2021 00:00:00</t>
+  </si>
+  <si>
+    <t>214243E2-BC05-F011-BAE2-002248A332C2</t>
+  </si>
+  <si>
+    <t>03/01/2021 00:00:00</t>
+  </si>
+  <si>
+    <t>Revenue_Results_Id</t>
+  </si>
+  <si>
+    <t>Invoice_Number</t>
+  </si>
+  <si>
+    <t>Total_Amount</t>
+  </si>
+  <si>
+    <t>EEC4924E-7C05-F011-BAE2-002248A332C2</t>
+  </si>
+  <si>
+    <t>09</t>
+  </si>
+  <si>
+    <t>Wahbi</t>
+  </si>
+  <si>
+    <t>EFC4924E-7C05-F011-BAE2-002248A332C2</t>
+  </si>
+  <si>
+    <t>Yosri</t>
+  </si>
+  <si>
+    <t>F0C4924E-7C05-F011-BAE2-002248A332C2</t>
+  </si>
+  <si>
+    <t>Syrin</t>
+  </si>
+  <si>
+    <t>F1C4924E-7C05-F011-BAE2-002248A332C2</t>
+  </si>
+  <si>
+    <t>Fadi</t>
+  </si>
+  <si>
+    <t>F2C4924E-7C05-F011-BAE2-002248A332C2</t>
+  </si>
+  <si>
+    <t>0A65B454-8105-F011-BAE2-002248A332C2</t>
+  </si>
+  <si>
+    <t>20/03/2025 11:49:08</t>
+  </si>
+  <si>
+    <t>Eima</t>
+  </si>
+  <si>
+    <t>B9A5CA61-8105-F011-BAE2-002248A332C2</t>
+  </si>
+  <si>
+    <t>20/03/2025 11:49:30</t>
+  </si>
+  <si>
+    <t>2022</t>
+  </si>
+  <si>
+    <t>08</t>
+  </si>
+  <si>
+    <t>Lamis</t>
+  </si>
+  <si>
+    <t>35AFBD70-8105-F011-BAE2-002248A332C2</t>
+  </si>
+  <si>
+    <t>20/03/2025 11:49:56</t>
+  </si>
+  <si>
+    <t>2027</t>
+  </si>
+  <si>
+    <t>04</t>
+  </si>
+  <si>
+    <t>Polo</t>
+  </si>
+  <si>
+    <t>224243E2-BC05-F011-BAE2-002248A332C2</t>
+  </si>
+  <si>
+    <t>20/03/2025 18:55:27</t>
+  </si>
+  <si>
+    <t>234243E2-BC05-F011-BAE2-002248A332C2</t>
+  </si>
+  <si>
+    <t>244243E2-BC05-F011-BAE2-002248A332C2</t>
+  </si>
+  <si>
+    <t>Monthly_Financial_Activities_Id</t>
+  </si>
+  <si>
+    <t>Bank_Fund</t>
+  </si>
+  <si>
+    <t>Total_Revenue</t>
+  </si>
+  <si>
+    <t>Total_Expenses</t>
+  </si>
+  <si>
+    <t>Rest</t>
+  </si>
+  <si>
+    <t>Global_Rest</t>
+  </si>
+  <si>
+    <t>Financial_Status</t>
+  </si>
+  <si>
+    <t>0DD62753-BA05-F011-BAE2-002248A332C2</t>
+  </si>
+  <si>
+    <t>20/03/2025 18:37:07</t>
+  </si>
+  <si>
+    <t>Good</t>
+  </si>
+  <si>
+    <t>DBC037E6-BD05-F011-BAE2-002248A332C2</t>
+  </si>
+  <si>
+    <t>20/03/2025 19:02:46</t>
+  </si>
+  <si>
+    <t>Critical</t>
+  </si>
+  <si>
+    <t>Annual_Financial_Activities_Id</t>
+  </si>
+  <si>
+    <t>D9F74407-0106-F011-BAE1-002248A332C2</t>
+  </si>
+  <si>
+    <t>21/03/2025 03:03:16</t>
+  </si>
+  <si>
+    <t>6F802885-829A-463A-A755-EC71DE9AFE2F</t>
+  </si>
+  <si>
+    <t>21/03/2025 03:01:17</t>
+  </si>
+  <si>
+    <t>2020</t>
+  </si>
+  <si>
+    <t>Bad</t>
+  </si>
+</sst>
+</file>
+
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
-<styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:x16r2="http://schemas.microsoft.com/office/spreadsheetml/2015/02/main" mc:Ignorable="x14ac x16r2">
-  <fonts count="1" x14ac:knownFonts="1">
+<styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:x16r2="http://schemas.microsoft.com/office/spreadsheetml/2015/02/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="x14ac x16r2 xr">
+  <fonts count="2" x14ac:knownFonts="1">
     <font>
       <sz val="11"/>
       <color theme="1"/>
       <name val="Calibri"/>
       <family val="2"/>
       <scheme val="minor"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <color indexed="8"/>
+      <name val="Calibri"/>
+      <family val="2"/>
     </font>
   </fonts>
   <fills count="2">
@@ -49,13 +648,2060 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="1">
+  <cellXfs count="2">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1"/>
   </cellXfs>
   <cellStyles count="1">
     <cellStyle name="Normal" xfId="0" builtinId="0"/>
   </cellStyles>
-  <dxfs count="0"/>
+  <dxfs count="76">
+    <dxf>
+      <font>
+        <b val="0"/>
+        <i val="0"/>
+        <strike val="0"/>
+        <condense val="0"/>
+        <extend val="0"/>
+        <outline val="0"/>
+        <shadow val="0"/>
+        <u val="none"/>
+        <vertAlign val="baseline"/>
+        <sz val="11"/>
+        <color indexed="8"/>
+        <name val="Calibri"/>
+        <family val="2"/>
+        <scheme val="none"/>
+      </font>
+      <numFmt numFmtId="0" formatCode="General"/>
+      <fill>
+        <patternFill patternType="none">
+          <fgColor indexed="64"/>
+          <bgColor indexed="65"/>
+        </patternFill>
+      </fill>
+      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="0" indent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
+      <protection locked="1" hidden="0"/>
+    </dxf>
+    <dxf>
+      <font>
+        <b val="0"/>
+        <i val="0"/>
+        <strike val="0"/>
+        <condense val="0"/>
+        <extend val="0"/>
+        <outline val="0"/>
+        <shadow val="0"/>
+        <u val="none"/>
+        <vertAlign val="baseline"/>
+        <sz val="11"/>
+        <color indexed="8"/>
+        <name val="Calibri"/>
+        <family val="2"/>
+        <scheme val="none"/>
+      </font>
+      <fill>
+        <patternFill patternType="none">
+          <fgColor indexed="64"/>
+          <bgColor indexed="65"/>
+        </patternFill>
+      </fill>
+      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="0" indent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
+      <protection locked="1" hidden="0"/>
+    </dxf>
+    <dxf>
+      <font>
+        <b val="0"/>
+        <i val="0"/>
+        <strike val="0"/>
+        <condense val="0"/>
+        <extend val="0"/>
+        <outline val="0"/>
+        <shadow val="0"/>
+        <u val="none"/>
+        <vertAlign val="baseline"/>
+        <sz val="11"/>
+        <color indexed="8"/>
+        <name val="Calibri"/>
+        <family val="2"/>
+        <scheme val="none"/>
+      </font>
+      <numFmt numFmtId="0" formatCode="General"/>
+      <fill>
+        <patternFill patternType="none">
+          <fgColor indexed="64"/>
+          <bgColor indexed="65"/>
+        </patternFill>
+      </fill>
+      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="0" indent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
+      <protection locked="1" hidden="0"/>
+    </dxf>
+    <dxf>
+      <font>
+        <b val="0"/>
+        <i val="0"/>
+        <strike val="0"/>
+        <condense val="0"/>
+        <extend val="0"/>
+        <outline val="0"/>
+        <shadow val="0"/>
+        <u val="none"/>
+        <vertAlign val="baseline"/>
+        <sz val="11"/>
+        <color indexed="8"/>
+        <name val="Calibri"/>
+        <family val="2"/>
+        <scheme val="none"/>
+      </font>
+      <numFmt numFmtId="0" formatCode="General"/>
+      <fill>
+        <patternFill patternType="none">
+          <fgColor indexed="64"/>
+          <bgColor indexed="65"/>
+        </patternFill>
+      </fill>
+      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="0" indent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
+      <protection locked="1" hidden="0"/>
+    </dxf>
+    <dxf>
+      <font>
+        <b val="0"/>
+        <i val="0"/>
+        <strike val="0"/>
+        <condense val="0"/>
+        <extend val="0"/>
+        <outline val="0"/>
+        <shadow val="0"/>
+        <u val="none"/>
+        <vertAlign val="baseline"/>
+        <sz val="11"/>
+        <color indexed="8"/>
+        <name val="Calibri"/>
+        <family val="2"/>
+        <scheme val="none"/>
+      </font>
+      <numFmt numFmtId="0" formatCode="General"/>
+      <fill>
+        <patternFill patternType="none">
+          <fgColor indexed="64"/>
+          <bgColor indexed="65"/>
+        </patternFill>
+      </fill>
+      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="0" indent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
+      <protection locked="1" hidden="0"/>
+    </dxf>
+    <dxf>
+      <font>
+        <b val="0"/>
+        <i val="0"/>
+        <strike val="0"/>
+        <condense val="0"/>
+        <extend val="0"/>
+        <outline val="0"/>
+        <shadow val="0"/>
+        <u val="none"/>
+        <vertAlign val="baseline"/>
+        <sz val="11"/>
+        <color indexed="8"/>
+        <name val="Calibri"/>
+        <family val="2"/>
+        <scheme val="none"/>
+      </font>
+      <numFmt numFmtId="0" formatCode="General"/>
+      <fill>
+        <patternFill patternType="none">
+          <fgColor indexed="64"/>
+          <bgColor indexed="65"/>
+        </patternFill>
+      </fill>
+      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="0" indent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
+      <protection locked="1" hidden="0"/>
+    </dxf>
+    <dxf>
+      <font>
+        <b val="0"/>
+        <i val="0"/>
+        <strike val="0"/>
+        <condense val="0"/>
+        <extend val="0"/>
+        <outline val="0"/>
+        <shadow val="0"/>
+        <u val="none"/>
+        <vertAlign val="baseline"/>
+        <sz val="11"/>
+        <color indexed="8"/>
+        <name val="Calibri"/>
+        <family val="2"/>
+        <scheme val="none"/>
+      </font>
+      <numFmt numFmtId="0" formatCode="General"/>
+      <fill>
+        <patternFill patternType="none">
+          <fgColor indexed="64"/>
+          <bgColor indexed="65"/>
+        </patternFill>
+      </fill>
+      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="0" indent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
+      <protection locked="1" hidden="0"/>
+    </dxf>
+    <dxf>
+      <font>
+        <b val="0"/>
+        <i val="0"/>
+        <strike val="0"/>
+        <condense val="0"/>
+        <extend val="0"/>
+        <outline val="0"/>
+        <shadow val="0"/>
+        <u val="none"/>
+        <vertAlign val="baseline"/>
+        <sz val="11"/>
+        <color indexed="8"/>
+        <name val="Calibri"/>
+        <family val="2"/>
+        <scheme val="none"/>
+      </font>
+      <numFmt numFmtId="0" formatCode="General"/>
+      <fill>
+        <patternFill patternType="none">
+          <fgColor indexed="64"/>
+          <bgColor indexed="65"/>
+        </patternFill>
+      </fill>
+      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="0" indent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
+      <protection locked="1" hidden="0"/>
+    </dxf>
+    <dxf>
+      <font>
+        <b val="0"/>
+        <i val="0"/>
+        <strike val="0"/>
+        <condense val="0"/>
+        <extend val="0"/>
+        <outline val="0"/>
+        <shadow val="0"/>
+        <u val="none"/>
+        <vertAlign val="baseline"/>
+        <sz val="11"/>
+        <color indexed="8"/>
+        <name val="Calibri"/>
+        <family val="2"/>
+        <scheme val="none"/>
+      </font>
+      <numFmt numFmtId="0" formatCode="General"/>
+      <fill>
+        <patternFill patternType="none">
+          <fgColor indexed="64"/>
+          <bgColor indexed="65"/>
+        </patternFill>
+      </fill>
+      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="0" indent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
+      <protection locked="1" hidden="0"/>
+    </dxf>
+    <dxf>
+      <font>
+        <b val="0"/>
+        <i val="0"/>
+        <strike val="0"/>
+        <condense val="0"/>
+        <extend val="0"/>
+        <outline val="0"/>
+        <shadow val="0"/>
+        <u val="none"/>
+        <vertAlign val="baseline"/>
+        <sz val="11"/>
+        <color indexed="8"/>
+        <name val="Calibri"/>
+        <family val="2"/>
+        <scheme val="none"/>
+      </font>
+      <numFmt numFmtId="0" formatCode="General"/>
+      <fill>
+        <patternFill patternType="none">
+          <fgColor indexed="64"/>
+          <bgColor indexed="65"/>
+        </patternFill>
+      </fill>
+      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="0" indent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
+      <protection locked="1" hidden="0"/>
+    </dxf>
+    <dxf>
+      <font>
+        <b val="0"/>
+        <i val="0"/>
+        <strike val="0"/>
+        <condense val="0"/>
+        <extend val="0"/>
+        <outline val="0"/>
+        <shadow val="0"/>
+        <u val="none"/>
+        <vertAlign val="baseline"/>
+        <sz val="11"/>
+        <color indexed="8"/>
+        <name val="Calibri"/>
+        <family val="2"/>
+        <scheme val="none"/>
+      </font>
+      <numFmt numFmtId="0" formatCode="General"/>
+      <fill>
+        <patternFill patternType="none">
+          <fgColor indexed="64"/>
+          <bgColor indexed="65"/>
+        </patternFill>
+      </fill>
+      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="0" indent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
+      <protection locked="1" hidden="0"/>
+    </dxf>
+    <dxf>
+      <font>
+        <b val="0"/>
+        <i val="0"/>
+        <strike val="0"/>
+        <condense val="0"/>
+        <extend val="0"/>
+        <outline val="0"/>
+        <shadow val="0"/>
+        <u val="none"/>
+        <vertAlign val="baseline"/>
+        <sz val="11"/>
+        <color indexed="8"/>
+        <name val="Calibri"/>
+        <family val="2"/>
+        <scheme val="none"/>
+      </font>
+      <numFmt numFmtId="0" formatCode="General"/>
+      <fill>
+        <patternFill patternType="none">
+          <fgColor indexed="64"/>
+          <bgColor indexed="65"/>
+        </patternFill>
+      </fill>
+      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="0" indent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
+      <protection locked="1" hidden="0"/>
+    </dxf>
+    <dxf>
+      <font>
+        <b val="0"/>
+        <i val="0"/>
+        <strike val="0"/>
+        <condense val="0"/>
+        <extend val="0"/>
+        <outline val="0"/>
+        <shadow val="0"/>
+        <u val="none"/>
+        <vertAlign val="baseline"/>
+        <sz val="11"/>
+        <color indexed="8"/>
+        <name val="Calibri"/>
+        <family val="2"/>
+        <scheme val="none"/>
+      </font>
+      <fill>
+        <patternFill patternType="none">
+          <fgColor indexed="64"/>
+          <bgColor indexed="65"/>
+        </patternFill>
+      </fill>
+      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="0" indent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
+      <protection locked="1" hidden="0"/>
+    </dxf>
+    <dxf>
+      <font>
+        <b val="0"/>
+        <i val="0"/>
+        <strike val="0"/>
+        <condense val="0"/>
+        <extend val="0"/>
+        <outline val="0"/>
+        <shadow val="0"/>
+        <u val="none"/>
+        <vertAlign val="baseline"/>
+        <sz val="11"/>
+        <color indexed="8"/>
+        <name val="Calibri"/>
+        <family val="2"/>
+        <scheme val="none"/>
+      </font>
+      <numFmt numFmtId="0" formatCode="General"/>
+      <fill>
+        <patternFill patternType="none">
+          <fgColor indexed="64"/>
+          <bgColor indexed="65"/>
+        </patternFill>
+      </fill>
+      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="0" indent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
+      <protection locked="1" hidden="0"/>
+    </dxf>
+    <dxf>
+      <font>
+        <b val="0"/>
+        <i val="0"/>
+        <strike val="0"/>
+        <condense val="0"/>
+        <extend val="0"/>
+        <outline val="0"/>
+        <shadow val="0"/>
+        <u val="none"/>
+        <vertAlign val="baseline"/>
+        <sz val="11"/>
+        <color indexed="8"/>
+        <name val="Calibri"/>
+        <family val="2"/>
+        <scheme val="none"/>
+      </font>
+      <numFmt numFmtId="0" formatCode="General"/>
+      <fill>
+        <patternFill patternType="none">
+          <fgColor indexed="64"/>
+          <bgColor indexed="65"/>
+        </patternFill>
+      </fill>
+      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="0" indent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
+      <protection locked="1" hidden="0"/>
+    </dxf>
+    <dxf>
+      <font>
+        <b val="0"/>
+        <i val="0"/>
+        <strike val="0"/>
+        <condense val="0"/>
+        <extend val="0"/>
+        <outline val="0"/>
+        <shadow val="0"/>
+        <u val="none"/>
+        <vertAlign val="baseline"/>
+        <sz val="11"/>
+        <color indexed="8"/>
+        <name val="Calibri"/>
+        <family val="2"/>
+        <scheme val="none"/>
+      </font>
+      <numFmt numFmtId="0" formatCode="General"/>
+      <fill>
+        <patternFill patternType="none">
+          <fgColor indexed="64"/>
+          <bgColor indexed="65"/>
+        </patternFill>
+      </fill>
+      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="0" indent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
+      <protection locked="1" hidden="0"/>
+    </dxf>
+    <dxf>
+      <font>
+        <b val="0"/>
+        <i val="0"/>
+        <strike val="0"/>
+        <condense val="0"/>
+        <extend val="0"/>
+        <outline val="0"/>
+        <shadow val="0"/>
+        <u val="none"/>
+        <vertAlign val="baseline"/>
+        <sz val="11"/>
+        <color indexed="8"/>
+        <name val="Calibri"/>
+        <family val="2"/>
+        <scheme val="none"/>
+      </font>
+      <numFmt numFmtId="0" formatCode="General"/>
+      <fill>
+        <patternFill patternType="none">
+          <fgColor indexed="64"/>
+          <bgColor indexed="65"/>
+        </patternFill>
+      </fill>
+      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="0" indent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
+      <protection locked="1" hidden="0"/>
+    </dxf>
+    <dxf>
+      <font>
+        <b val="0"/>
+        <i val="0"/>
+        <strike val="0"/>
+        <condense val="0"/>
+        <extend val="0"/>
+        <outline val="0"/>
+        <shadow val="0"/>
+        <u val="none"/>
+        <vertAlign val="baseline"/>
+        <sz val="11"/>
+        <color indexed="8"/>
+        <name val="Calibri"/>
+        <family val="2"/>
+        <scheme val="none"/>
+      </font>
+      <numFmt numFmtId="0" formatCode="General"/>
+      <fill>
+        <patternFill patternType="none">
+          <fgColor indexed="64"/>
+          <bgColor indexed="65"/>
+        </patternFill>
+      </fill>
+      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="0" indent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
+      <protection locked="1" hidden="0"/>
+    </dxf>
+    <dxf>
+      <font>
+        <b val="0"/>
+        <i val="0"/>
+        <strike val="0"/>
+        <condense val="0"/>
+        <extend val="0"/>
+        <outline val="0"/>
+        <shadow val="0"/>
+        <u val="none"/>
+        <vertAlign val="baseline"/>
+        <sz val="11"/>
+        <color indexed="8"/>
+        <name val="Calibri"/>
+        <family val="2"/>
+        <scheme val="none"/>
+      </font>
+      <numFmt numFmtId="0" formatCode="General"/>
+      <fill>
+        <patternFill patternType="none">
+          <fgColor indexed="64"/>
+          <bgColor indexed="65"/>
+        </patternFill>
+      </fill>
+      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="0" indent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
+      <protection locked="1" hidden="0"/>
+    </dxf>
+    <dxf>
+      <font>
+        <b val="0"/>
+        <i val="0"/>
+        <strike val="0"/>
+        <condense val="0"/>
+        <extend val="0"/>
+        <outline val="0"/>
+        <shadow val="0"/>
+        <u val="none"/>
+        <vertAlign val="baseline"/>
+        <sz val="11"/>
+        <color indexed="8"/>
+        <name val="Calibri"/>
+        <family val="2"/>
+        <scheme val="none"/>
+      </font>
+      <numFmt numFmtId="0" formatCode="General"/>
+      <fill>
+        <patternFill patternType="none">
+          <fgColor indexed="64"/>
+          <bgColor indexed="65"/>
+        </patternFill>
+      </fill>
+      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="0" indent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
+      <protection locked="1" hidden="0"/>
+    </dxf>
+    <dxf>
+      <font>
+        <b val="0"/>
+        <i val="0"/>
+        <strike val="0"/>
+        <condense val="0"/>
+        <extend val="0"/>
+        <outline val="0"/>
+        <shadow val="0"/>
+        <u val="none"/>
+        <vertAlign val="baseline"/>
+        <sz val="11"/>
+        <color indexed="8"/>
+        <name val="Calibri"/>
+        <family val="2"/>
+        <scheme val="none"/>
+      </font>
+      <numFmt numFmtId="0" formatCode="General"/>
+      <fill>
+        <patternFill patternType="none">
+          <fgColor indexed="64"/>
+          <bgColor indexed="65"/>
+        </patternFill>
+      </fill>
+      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="0" indent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
+      <protection locked="1" hidden="0"/>
+    </dxf>
+    <dxf>
+      <font>
+        <b val="0"/>
+        <i val="0"/>
+        <strike val="0"/>
+        <condense val="0"/>
+        <extend val="0"/>
+        <outline val="0"/>
+        <shadow val="0"/>
+        <u val="none"/>
+        <vertAlign val="baseline"/>
+        <sz val="11"/>
+        <color indexed="8"/>
+        <name val="Calibri"/>
+        <family val="2"/>
+        <scheme val="none"/>
+      </font>
+      <numFmt numFmtId="0" formatCode="General"/>
+      <fill>
+        <patternFill patternType="none">
+          <fgColor indexed="64"/>
+          <bgColor indexed="65"/>
+        </patternFill>
+      </fill>
+      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="0" indent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
+      <protection locked="1" hidden="0"/>
+    </dxf>
+    <dxf>
+      <font>
+        <b val="0"/>
+        <i val="0"/>
+        <strike val="0"/>
+        <condense val="0"/>
+        <extend val="0"/>
+        <outline val="0"/>
+        <shadow val="0"/>
+        <u val="none"/>
+        <vertAlign val="baseline"/>
+        <sz val="11"/>
+        <color indexed="8"/>
+        <name val="Calibri"/>
+        <family val="2"/>
+        <scheme val="none"/>
+      </font>
+      <numFmt numFmtId="0" formatCode="General"/>
+      <fill>
+        <patternFill patternType="none">
+          <fgColor indexed="64"/>
+          <bgColor indexed="65"/>
+        </patternFill>
+      </fill>
+      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="0" indent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
+      <protection locked="1" hidden="0"/>
+    </dxf>
+    <dxf>
+      <font>
+        <b val="0"/>
+        <i val="0"/>
+        <strike val="0"/>
+        <condense val="0"/>
+        <extend val="0"/>
+        <outline val="0"/>
+        <shadow val="0"/>
+        <u val="none"/>
+        <vertAlign val="baseline"/>
+        <sz val="11"/>
+        <color indexed="8"/>
+        <name val="Calibri"/>
+        <family val="2"/>
+        <scheme val="none"/>
+      </font>
+      <numFmt numFmtId="0" formatCode="General"/>
+      <fill>
+        <patternFill patternType="none">
+          <fgColor indexed="64"/>
+          <bgColor indexed="65"/>
+        </patternFill>
+      </fill>
+      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="0" indent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
+      <protection locked="1" hidden="0"/>
+    </dxf>
+    <dxf>
+      <font>
+        <b val="0"/>
+        <i val="0"/>
+        <strike val="0"/>
+        <condense val="0"/>
+        <extend val="0"/>
+        <outline val="0"/>
+        <shadow val="0"/>
+        <u val="none"/>
+        <vertAlign val="baseline"/>
+        <sz val="11"/>
+        <color indexed="8"/>
+        <name val="Calibri"/>
+        <family val="2"/>
+        <scheme val="none"/>
+      </font>
+      <fill>
+        <patternFill patternType="none">
+          <fgColor indexed="64"/>
+          <bgColor indexed="65"/>
+        </patternFill>
+      </fill>
+      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="0" indent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
+      <protection locked="1" hidden="0"/>
+    </dxf>
+    <dxf>
+      <font>
+        <b val="0"/>
+        <i val="0"/>
+        <strike val="0"/>
+        <condense val="0"/>
+        <extend val="0"/>
+        <outline val="0"/>
+        <shadow val="0"/>
+        <u val="none"/>
+        <vertAlign val="baseline"/>
+        <sz val="11"/>
+        <color indexed="8"/>
+        <name val="Calibri"/>
+        <family val="2"/>
+        <scheme val="none"/>
+      </font>
+      <numFmt numFmtId="0" formatCode="General"/>
+      <fill>
+        <patternFill patternType="none">
+          <fgColor indexed="64"/>
+          <bgColor indexed="65"/>
+        </patternFill>
+      </fill>
+      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="0" indent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
+      <protection locked="1" hidden="0"/>
+    </dxf>
+    <dxf>
+      <font>
+        <b val="0"/>
+        <i val="0"/>
+        <strike val="0"/>
+        <condense val="0"/>
+        <extend val="0"/>
+        <outline val="0"/>
+        <shadow val="0"/>
+        <u val="none"/>
+        <vertAlign val="baseline"/>
+        <sz val="11"/>
+        <color indexed="8"/>
+        <name val="Calibri"/>
+        <family val="2"/>
+        <scheme val="none"/>
+      </font>
+      <numFmt numFmtId="0" formatCode="General"/>
+      <fill>
+        <patternFill patternType="none">
+          <fgColor indexed="64"/>
+          <bgColor indexed="65"/>
+        </patternFill>
+      </fill>
+      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="0" indent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
+      <protection locked="1" hidden="0"/>
+    </dxf>
+    <dxf>
+      <font>
+        <b val="0"/>
+        <i val="0"/>
+        <strike val="0"/>
+        <condense val="0"/>
+        <extend val="0"/>
+        <outline val="0"/>
+        <shadow val="0"/>
+        <u val="none"/>
+        <vertAlign val="baseline"/>
+        <sz val="11"/>
+        <color indexed="8"/>
+        <name val="Calibri"/>
+        <family val="2"/>
+        <scheme val="none"/>
+      </font>
+      <numFmt numFmtId="0" formatCode="General"/>
+      <fill>
+        <patternFill patternType="none">
+          <fgColor indexed="64"/>
+          <bgColor indexed="65"/>
+        </patternFill>
+      </fill>
+      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="0" indent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
+      <protection locked="1" hidden="0"/>
+    </dxf>
+    <dxf>
+      <font>
+        <b val="0"/>
+        <i val="0"/>
+        <strike val="0"/>
+        <condense val="0"/>
+        <extend val="0"/>
+        <outline val="0"/>
+        <shadow val="0"/>
+        <u val="none"/>
+        <vertAlign val="baseline"/>
+        <sz val="11"/>
+        <color indexed="8"/>
+        <name val="Calibri"/>
+        <family val="2"/>
+        <scheme val="none"/>
+      </font>
+      <numFmt numFmtId="0" formatCode="General"/>
+      <fill>
+        <patternFill patternType="none">
+          <fgColor indexed="64"/>
+          <bgColor indexed="65"/>
+        </patternFill>
+      </fill>
+      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="0" indent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
+      <protection locked="1" hidden="0"/>
+    </dxf>
+    <dxf>
+      <font>
+        <b val="0"/>
+        <i val="0"/>
+        <strike val="0"/>
+        <condense val="0"/>
+        <extend val="0"/>
+        <outline val="0"/>
+        <shadow val="0"/>
+        <u val="none"/>
+        <vertAlign val="baseline"/>
+        <sz val="11"/>
+        <color indexed="8"/>
+        <name val="Calibri"/>
+        <family val="2"/>
+        <scheme val="none"/>
+      </font>
+      <numFmt numFmtId="0" formatCode="General"/>
+      <fill>
+        <patternFill patternType="none">
+          <fgColor indexed="64"/>
+          <bgColor indexed="65"/>
+        </patternFill>
+      </fill>
+      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="0" indent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
+      <protection locked="1" hidden="0"/>
+    </dxf>
+    <dxf>
+      <font>
+        <b val="0"/>
+        <i val="0"/>
+        <strike val="0"/>
+        <condense val="0"/>
+        <extend val="0"/>
+        <outline val="0"/>
+        <shadow val="0"/>
+        <u val="none"/>
+        <vertAlign val="baseline"/>
+        <sz val="11"/>
+        <color indexed="8"/>
+        <name val="Calibri"/>
+        <family val="2"/>
+        <scheme val="none"/>
+      </font>
+      <numFmt numFmtId="0" formatCode="General"/>
+      <fill>
+        <patternFill patternType="none">
+          <fgColor indexed="64"/>
+          <bgColor indexed="65"/>
+        </patternFill>
+      </fill>
+      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="0" indent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
+      <protection locked="1" hidden="0"/>
+    </dxf>
+    <dxf>
+      <font>
+        <b val="0"/>
+        <i val="0"/>
+        <strike val="0"/>
+        <condense val="0"/>
+        <extend val="0"/>
+        <outline val="0"/>
+        <shadow val="0"/>
+        <u val="none"/>
+        <vertAlign val="baseline"/>
+        <sz val="11"/>
+        <color indexed="8"/>
+        <name val="Calibri"/>
+        <family val="2"/>
+        <scheme val="none"/>
+      </font>
+      <numFmt numFmtId="0" formatCode="General"/>
+      <fill>
+        <patternFill patternType="none">
+          <fgColor indexed="64"/>
+          <bgColor indexed="65"/>
+        </patternFill>
+      </fill>
+      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="0" indent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
+      <protection locked="1" hidden="0"/>
+    </dxf>
+    <dxf>
+      <font>
+        <b val="0"/>
+        <i val="0"/>
+        <strike val="0"/>
+        <condense val="0"/>
+        <extend val="0"/>
+        <outline val="0"/>
+        <shadow val="0"/>
+        <u val="none"/>
+        <vertAlign val="baseline"/>
+        <sz val="11"/>
+        <color indexed="8"/>
+        <name val="Calibri"/>
+        <family val="2"/>
+        <scheme val="none"/>
+      </font>
+      <numFmt numFmtId="0" formatCode="General"/>
+      <fill>
+        <patternFill patternType="none">
+          <fgColor indexed="64"/>
+          <bgColor indexed="65"/>
+        </patternFill>
+      </fill>
+      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="0" indent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
+      <protection locked="1" hidden="0"/>
+    </dxf>
+    <dxf>
+      <font>
+        <b val="0"/>
+        <i val="0"/>
+        <strike val="0"/>
+        <condense val="0"/>
+        <extend val="0"/>
+        <outline val="0"/>
+        <shadow val="0"/>
+        <u val="none"/>
+        <vertAlign val="baseline"/>
+        <sz val="11"/>
+        <color indexed="8"/>
+        <name val="Calibri"/>
+        <family val="2"/>
+        <scheme val="none"/>
+      </font>
+      <fill>
+        <patternFill patternType="none">
+          <fgColor indexed="64"/>
+          <bgColor indexed="65"/>
+        </patternFill>
+      </fill>
+      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="0" indent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
+      <protection locked="1" hidden="0"/>
+    </dxf>
+    <dxf>
+      <font>
+        <b val="0"/>
+        <i val="0"/>
+        <strike val="0"/>
+        <condense val="0"/>
+        <extend val="0"/>
+        <outline val="0"/>
+        <shadow val="0"/>
+        <u val="none"/>
+        <vertAlign val="baseline"/>
+        <sz val="11"/>
+        <color indexed="8"/>
+        <name val="Calibri"/>
+        <family val="2"/>
+        <scheme val="none"/>
+      </font>
+      <numFmt numFmtId="0" formatCode="General"/>
+      <fill>
+        <patternFill patternType="none">
+          <fgColor indexed="64"/>
+          <bgColor indexed="65"/>
+        </patternFill>
+      </fill>
+      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="0" indent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
+      <protection locked="1" hidden="0"/>
+    </dxf>
+    <dxf>
+      <font>
+        <b val="0"/>
+        <i val="0"/>
+        <strike val="0"/>
+        <condense val="0"/>
+        <extend val="0"/>
+        <outline val="0"/>
+        <shadow val="0"/>
+        <u val="none"/>
+        <vertAlign val="baseline"/>
+        <sz val="11"/>
+        <color indexed="8"/>
+        <name val="Calibri"/>
+        <family val="2"/>
+        <scheme val="none"/>
+      </font>
+      <numFmt numFmtId="0" formatCode="General"/>
+      <fill>
+        <patternFill patternType="none">
+          <fgColor indexed="64"/>
+          <bgColor indexed="65"/>
+        </patternFill>
+      </fill>
+      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="0" indent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
+      <protection locked="1" hidden="0"/>
+    </dxf>
+    <dxf>
+      <font>
+        <b val="0"/>
+        <i val="0"/>
+        <strike val="0"/>
+        <condense val="0"/>
+        <extend val="0"/>
+        <outline val="0"/>
+        <shadow val="0"/>
+        <u val="none"/>
+        <vertAlign val="baseline"/>
+        <sz val="11"/>
+        <color indexed="8"/>
+        <name val="Calibri"/>
+        <family val="2"/>
+        <scheme val="none"/>
+      </font>
+      <numFmt numFmtId="0" formatCode="General"/>
+      <fill>
+        <patternFill patternType="none">
+          <fgColor indexed="64"/>
+          <bgColor indexed="65"/>
+        </patternFill>
+      </fill>
+      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="0" indent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
+      <protection locked="1" hidden="0"/>
+    </dxf>
+    <dxf>
+      <font>
+        <b val="0"/>
+        <i val="0"/>
+        <strike val="0"/>
+        <condense val="0"/>
+        <extend val="0"/>
+        <outline val="0"/>
+        <shadow val="0"/>
+        <u val="none"/>
+        <vertAlign val="baseline"/>
+        <sz val="11"/>
+        <color indexed="8"/>
+        <name val="Calibri"/>
+        <family val="2"/>
+        <scheme val="none"/>
+      </font>
+      <numFmt numFmtId="0" formatCode="General"/>
+      <fill>
+        <patternFill patternType="none">
+          <fgColor indexed="64"/>
+          <bgColor indexed="65"/>
+        </patternFill>
+      </fill>
+      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="0" indent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
+      <protection locked="1" hidden="0"/>
+    </dxf>
+    <dxf>
+      <font>
+        <b val="0"/>
+        <i val="0"/>
+        <strike val="0"/>
+        <condense val="0"/>
+        <extend val="0"/>
+        <outline val="0"/>
+        <shadow val="0"/>
+        <u val="none"/>
+        <vertAlign val="baseline"/>
+        <sz val="11"/>
+        <color indexed="8"/>
+        <name val="Calibri"/>
+        <family val="2"/>
+        <scheme val="none"/>
+      </font>
+      <numFmt numFmtId="0" formatCode="General"/>
+      <fill>
+        <patternFill patternType="none">
+          <fgColor indexed="64"/>
+          <bgColor indexed="65"/>
+        </patternFill>
+      </fill>
+      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="0" indent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
+      <protection locked="1" hidden="0"/>
+    </dxf>
+    <dxf>
+      <font>
+        <b val="0"/>
+        <i val="0"/>
+        <strike val="0"/>
+        <condense val="0"/>
+        <extend val="0"/>
+        <outline val="0"/>
+        <shadow val="0"/>
+        <u val="none"/>
+        <vertAlign val="baseline"/>
+        <sz val="11"/>
+        <color indexed="8"/>
+        <name val="Calibri"/>
+        <family val="2"/>
+        <scheme val="none"/>
+      </font>
+      <numFmt numFmtId="0" formatCode="General"/>
+      <fill>
+        <patternFill patternType="none">
+          <fgColor indexed="64"/>
+          <bgColor indexed="65"/>
+        </patternFill>
+      </fill>
+      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="0" indent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
+      <protection locked="1" hidden="0"/>
+    </dxf>
+    <dxf>
+      <font>
+        <b val="0"/>
+        <i val="0"/>
+        <strike val="0"/>
+        <condense val="0"/>
+        <extend val="0"/>
+        <outline val="0"/>
+        <shadow val="0"/>
+        <u val="none"/>
+        <vertAlign val="baseline"/>
+        <sz val="11"/>
+        <color indexed="8"/>
+        <name val="Calibri"/>
+        <family val="2"/>
+        <scheme val="none"/>
+      </font>
+      <numFmt numFmtId="0" formatCode="General"/>
+      <fill>
+        <patternFill patternType="none">
+          <fgColor indexed="64"/>
+          <bgColor indexed="65"/>
+        </patternFill>
+      </fill>
+      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="0" indent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
+      <protection locked="1" hidden="0"/>
+    </dxf>
+    <dxf>
+      <font>
+        <b val="0"/>
+        <i val="0"/>
+        <strike val="0"/>
+        <condense val="0"/>
+        <extend val="0"/>
+        <outline val="0"/>
+        <shadow val="0"/>
+        <u val="none"/>
+        <vertAlign val="baseline"/>
+        <sz val="11"/>
+        <color indexed="8"/>
+        <name val="Calibri"/>
+        <family val="2"/>
+        <scheme val="none"/>
+      </font>
+      <fill>
+        <patternFill patternType="none">
+          <fgColor indexed="64"/>
+          <bgColor indexed="65"/>
+        </patternFill>
+      </fill>
+      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="0" indent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
+      <protection locked="1" hidden="0"/>
+    </dxf>
+    <dxf>
+      <font>
+        <b val="0"/>
+        <i val="0"/>
+        <strike val="0"/>
+        <condense val="0"/>
+        <extend val="0"/>
+        <outline val="0"/>
+        <shadow val="0"/>
+        <u val="none"/>
+        <vertAlign val="baseline"/>
+        <sz val="11"/>
+        <color indexed="8"/>
+        <name val="Calibri"/>
+        <family val="2"/>
+        <scheme val="none"/>
+      </font>
+      <numFmt numFmtId="0" formatCode="General"/>
+      <fill>
+        <patternFill patternType="none">
+          <fgColor indexed="64"/>
+          <bgColor indexed="65"/>
+        </patternFill>
+      </fill>
+      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="0" indent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
+      <protection locked="1" hidden="0"/>
+    </dxf>
+    <dxf>
+      <font>
+        <b val="0"/>
+        <i val="0"/>
+        <strike val="0"/>
+        <condense val="0"/>
+        <extend val="0"/>
+        <outline val="0"/>
+        <shadow val="0"/>
+        <u val="none"/>
+        <vertAlign val="baseline"/>
+        <sz val="11"/>
+        <color indexed="8"/>
+        <name val="Calibri"/>
+        <family val="2"/>
+        <scheme val="none"/>
+      </font>
+      <numFmt numFmtId="0" formatCode="General"/>
+      <fill>
+        <patternFill patternType="none">
+          <fgColor indexed="64"/>
+          <bgColor indexed="65"/>
+        </patternFill>
+      </fill>
+      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="0" indent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
+      <protection locked="1" hidden="0"/>
+    </dxf>
+    <dxf>
+      <font>
+        <b val="0"/>
+        <i val="0"/>
+        <strike val="0"/>
+        <condense val="0"/>
+        <extend val="0"/>
+        <outline val="0"/>
+        <shadow val="0"/>
+        <u val="none"/>
+        <vertAlign val="baseline"/>
+        <sz val="11"/>
+        <color indexed="8"/>
+        <name val="Calibri"/>
+        <family val="2"/>
+        <scheme val="none"/>
+      </font>
+      <numFmt numFmtId="0" formatCode="General"/>
+      <fill>
+        <patternFill patternType="none">
+          <fgColor indexed="64"/>
+          <bgColor indexed="65"/>
+        </patternFill>
+      </fill>
+      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="0" indent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
+      <protection locked="1" hidden="0"/>
+    </dxf>
+    <dxf>
+      <font>
+        <b val="0"/>
+        <i val="0"/>
+        <strike val="0"/>
+        <condense val="0"/>
+        <extend val="0"/>
+        <outline val="0"/>
+        <shadow val="0"/>
+        <u val="none"/>
+        <vertAlign val="baseline"/>
+        <sz val="11"/>
+        <color indexed="8"/>
+        <name val="Calibri"/>
+        <family val="2"/>
+        <scheme val="none"/>
+      </font>
+      <numFmt numFmtId="0" formatCode="General"/>
+      <fill>
+        <patternFill patternType="none">
+          <fgColor indexed="64"/>
+          <bgColor indexed="65"/>
+        </patternFill>
+      </fill>
+      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="0" indent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
+      <protection locked="1" hidden="0"/>
+    </dxf>
+    <dxf>
+      <font>
+        <b val="0"/>
+        <i val="0"/>
+        <strike val="0"/>
+        <condense val="0"/>
+        <extend val="0"/>
+        <outline val="0"/>
+        <shadow val="0"/>
+        <u val="none"/>
+        <vertAlign val="baseline"/>
+        <sz val="11"/>
+        <color indexed="8"/>
+        <name val="Calibri"/>
+        <family val="2"/>
+        <scheme val="none"/>
+      </font>
+      <numFmt numFmtId="0" formatCode="General"/>
+      <fill>
+        <patternFill patternType="none">
+          <fgColor indexed="64"/>
+          <bgColor indexed="65"/>
+        </patternFill>
+      </fill>
+      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="0" indent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
+      <protection locked="1" hidden="0"/>
+    </dxf>
+    <dxf>
+      <font>
+        <b val="0"/>
+        <i val="0"/>
+        <strike val="0"/>
+        <condense val="0"/>
+        <extend val="0"/>
+        <outline val="0"/>
+        <shadow val="0"/>
+        <u val="none"/>
+        <vertAlign val="baseline"/>
+        <sz val="11"/>
+        <color indexed="8"/>
+        <name val="Calibri"/>
+        <family val="2"/>
+        <scheme val="none"/>
+      </font>
+      <numFmt numFmtId="0" formatCode="General"/>
+      <fill>
+        <patternFill patternType="none">
+          <fgColor indexed="64"/>
+          <bgColor indexed="65"/>
+        </patternFill>
+      </fill>
+      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="0" indent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
+      <protection locked="1" hidden="0"/>
+    </dxf>
+    <dxf>
+      <font>
+        <b val="0"/>
+        <i val="0"/>
+        <strike val="0"/>
+        <condense val="0"/>
+        <extend val="0"/>
+        <outline val="0"/>
+        <shadow val="0"/>
+        <u val="none"/>
+        <vertAlign val="baseline"/>
+        <sz val="11"/>
+        <color indexed="8"/>
+        <name val="Calibri"/>
+        <family val="2"/>
+        <scheme val="none"/>
+      </font>
+      <numFmt numFmtId="0" formatCode="General"/>
+      <fill>
+        <patternFill patternType="none">
+          <fgColor indexed="64"/>
+          <bgColor indexed="65"/>
+        </patternFill>
+      </fill>
+      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="0" indent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
+      <protection locked="1" hidden="0"/>
+    </dxf>
+    <dxf>
+      <font>
+        <b val="0"/>
+        <i val="0"/>
+        <strike val="0"/>
+        <condense val="0"/>
+        <extend val="0"/>
+        <outline val="0"/>
+        <shadow val="0"/>
+        <u val="none"/>
+        <vertAlign val="baseline"/>
+        <sz val="11"/>
+        <color indexed="8"/>
+        <name val="Calibri"/>
+        <family val="2"/>
+        <scheme val="none"/>
+      </font>
+      <numFmt numFmtId="0" formatCode="General"/>
+      <fill>
+        <patternFill patternType="none">
+          <fgColor indexed="64"/>
+          <bgColor indexed="65"/>
+        </patternFill>
+      </fill>
+      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="0" indent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
+      <protection locked="1" hidden="0"/>
+    </dxf>
+    <dxf>
+      <font>
+        <b val="0"/>
+        <i val="0"/>
+        <strike val="0"/>
+        <condense val="0"/>
+        <extend val="0"/>
+        <outline val="0"/>
+        <shadow val="0"/>
+        <u val="none"/>
+        <vertAlign val="baseline"/>
+        <sz val="11"/>
+        <color indexed="8"/>
+        <name val="Calibri"/>
+        <family val="2"/>
+        <scheme val="none"/>
+      </font>
+      <numFmt numFmtId="0" formatCode="General"/>
+      <fill>
+        <patternFill patternType="none">
+          <fgColor indexed="64"/>
+          <bgColor indexed="65"/>
+        </patternFill>
+      </fill>
+      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="0" indent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
+      <protection locked="1" hidden="0"/>
+    </dxf>
+    <dxf>
+      <font>
+        <b val="0"/>
+        <i val="0"/>
+        <strike val="0"/>
+        <condense val="0"/>
+        <extend val="0"/>
+        <outline val="0"/>
+        <shadow val="0"/>
+        <u val="none"/>
+        <vertAlign val="baseline"/>
+        <sz val="11"/>
+        <color indexed="8"/>
+        <name val="Calibri"/>
+        <family val="2"/>
+        <scheme val="none"/>
+      </font>
+      <numFmt numFmtId="0" formatCode="General"/>
+      <fill>
+        <patternFill patternType="none">
+          <fgColor indexed="64"/>
+          <bgColor indexed="65"/>
+        </patternFill>
+      </fill>
+      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="0" indent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
+      <protection locked="1" hidden="0"/>
+    </dxf>
+    <dxf>
+      <font>
+        <b val="0"/>
+        <i val="0"/>
+        <strike val="0"/>
+        <condense val="0"/>
+        <extend val="0"/>
+        <outline val="0"/>
+        <shadow val="0"/>
+        <u val="none"/>
+        <vertAlign val="baseline"/>
+        <sz val="11"/>
+        <color indexed="8"/>
+        <name val="Calibri"/>
+        <family val="2"/>
+        <scheme val="none"/>
+      </font>
+      <numFmt numFmtId="0" formatCode="General"/>
+      <fill>
+        <patternFill patternType="none">
+          <fgColor indexed="64"/>
+          <bgColor indexed="65"/>
+        </patternFill>
+      </fill>
+      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="0" indent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
+      <protection locked="1" hidden="0"/>
+    </dxf>
+    <dxf>
+      <font>
+        <b val="0"/>
+        <i val="0"/>
+        <strike val="0"/>
+        <condense val="0"/>
+        <extend val="0"/>
+        <outline val="0"/>
+        <shadow val="0"/>
+        <u val="none"/>
+        <vertAlign val="baseline"/>
+        <sz val="11"/>
+        <color indexed="8"/>
+        <name val="Calibri"/>
+        <family val="2"/>
+        <scheme val="none"/>
+      </font>
+      <fill>
+        <patternFill patternType="none">
+          <fgColor indexed="64"/>
+          <bgColor indexed="65"/>
+        </patternFill>
+      </fill>
+      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="0" indent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
+      <protection locked="1" hidden="0"/>
+    </dxf>
+    <dxf>
+      <font>
+        <b val="0"/>
+        <i val="0"/>
+        <strike val="0"/>
+        <condense val="0"/>
+        <extend val="0"/>
+        <outline val="0"/>
+        <shadow val="0"/>
+        <u val="none"/>
+        <vertAlign val="baseline"/>
+        <sz val="11"/>
+        <color indexed="8"/>
+        <name val="Calibri"/>
+        <family val="2"/>
+        <scheme val="none"/>
+      </font>
+      <numFmt numFmtId="0" formatCode="General"/>
+      <fill>
+        <patternFill patternType="none">
+          <fgColor indexed="64"/>
+          <bgColor indexed="65"/>
+        </patternFill>
+      </fill>
+      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="0" indent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
+      <protection locked="1" hidden="0"/>
+    </dxf>
+    <dxf>
+      <font>
+        <b val="0"/>
+        <i val="0"/>
+        <strike val="0"/>
+        <condense val="0"/>
+        <extend val="0"/>
+        <outline val="0"/>
+        <shadow val="0"/>
+        <u val="none"/>
+        <vertAlign val="baseline"/>
+        <sz val="11"/>
+        <color indexed="8"/>
+        <name val="Calibri"/>
+        <family val="2"/>
+        <scheme val="none"/>
+      </font>
+      <numFmt numFmtId="0" formatCode="General"/>
+      <fill>
+        <patternFill patternType="none">
+          <fgColor indexed="64"/>
+          <bgColor indexed="65"/>
+        </patternFill>
+      </fill>
+      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="0" indent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
+      <protection locked="1" hidden="0"/>
+    </dxf>
+    <dxf>
+      <font>
+        <b val="0"/>
+        <i val="0"/>
+        <strike val="0"/>
+        <condense val="0"/>
+        <extend val="0"/>
+        <outline val="0"/>
+        <shadow val="0"/>
+        <u val="none"/>
+        <vertAlign val="baseline"/>
+        <sz val="11"/>
+        <color indexed="8"/>
+        <name val="Calibri"/>
+        <family val="2"/>
+        <scheme val="none"/>
+      </font>
+      <numFmt numFmtId="0" formatCode="General"/>
+      <fill>
+        <patternFill patternType="none">
+          <fgColor indexed="64"/>
+          <bgColor indexed="65"/>
+        </patternFill>
+      </fill>
+      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="0" indent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
+      <protection locked="1" hidden="0"/>
+    </dxf>
+    <dxf>
+      <font>
+        <b val="0"/>
+        <i val="0"/>
+        <strike val="0"/>
+        <condense val="0"/>
+        <extend val="0"/>
+        <outline val="0"/>
+        <shadow val="0"/>
+        <u val="none"/>
+        <vertAlign val="baseline"/>
+        <sz val="11"/>
+        <color indexed="8"/>
+        <name val="Calibri"/>
+        <family val="2"/>
+        <scheme val="none"/>
+      </font>
+      <numFmt numFmtId="0" formatCode="General"/>
+      <fill>
+        <patternFill patternType="none">
+          <fgColor indexed="64"/>
+          <bgColor indexed="65"/>
+        </patternFill>
+      </fill>
+      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="0" indent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
+      <protection locked="1" hidden="0"/>
+    </dxf>
+    <dxf>
+      <font>
+        <b val="0"/>
+        <i val="0"/>
+        <strike val="0"/>
+        <condense val="0"/>
+        <extend val="0"/>
+        <outline val="0"/>
+        <shadow val="0"/>
+        <u val="none"/>
+        <vertAlign val="baseline"/>
+        <sz val="11"/>
+        <color indexed="8"/>
+        <name val="Calibri"/>
+        <family val="2"/>
+        <scheme val="none"/>
+      </font>
+      <numFmt numFmtId="0" formatCode="General"/>
+      <fill>
+        <patternFill patternType="none">
+          <fgColor indexed="64"/>
+          <bgColor indexed="65"/>
+        </patternFill>
+      </fill>
+      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="0" indent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
+      <protection locked="1" hidden="0"/>
+    </dxf>
+    <dxf>
+      <font>
+        <b val="0"/>
+        <i val="0"/>
+        <strike val="0"/>
+        <condense val="0"/>
+        <extend val="0"/>
+        <outline val="0"/>
+        <shadow val="0"/>
+        <u val="none"/>
+        <vertAlign val="baseline"/>
+        <sz val="11"/>
+        <color indexed="8"/>
+        <name val="Calibri"/>
+        <family val="2"/>
+        <scheme val="none"/>
+      </font>
+      <numFmt numFmtId="0" formatCode="General"/>
+      <fill>
+        <patternFill patternType="none">
+          <fgColor indexed="64"/>
+          <bgColor indexed="65"/>
+        </patternFill>
+      </fill>
+      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="0" indent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
+      <protection locked="1" hidden="0"/>
+    </dxf>
+    <dxf>
+      <font>
+        <b val="0"/>
+        <i val="0"/>
+        <strike val="0"/>
+        <condense val="0"/>
+        <extend val="0"/>
+        <outline val="0"/>
+        <shadow val="0"/>
+        <u val="none"/>
+        <vertAlign val="baseline"/>
+        <sz val="11"/>
+        <color indexed="8"/>
+        <name val="Calibri"/>
+        <family val="2"/>
+        <scheme val="none"/>
+      </font>
+      <numFmt numFmtId="0" formatCode="General"/>
+      <fill>
+        <patternFill patternType="none">
+          <fgColor indexed="64"/>
+          <bgColor indexed="65"/>
+        </patternFill>
+      </fill>
+      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="0" indent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
+      <protection locked="1" hidden="0"/>
+    </dxf>
+    <dxf>
+      <font>
+        <b val="0"/>
+        <i val="0"/>
+        <strike val="0"/>
+        <condense val="0"/>
+        <extend val="0"/>
+        <outline val="0"/>
+        <shadow val="0"/>
+        <u val="none"/>
+        <vertAlign val="baseline"/>
+        <sz val="11"/>
+        <color indexed="8"/>
+        <name val="Calibri"/>
+        <family val="2"/>
+        <scheme val="none"/>
+      </font>
+      <fill>
+        <patternFill patternType="none">
+          <fgColor indexed="64"/>
+          <bgColor indexed="65"/>
+        </patternFill>
+      </fill>
+      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="0" indent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
+      <protection locked="1" hidden="0"/>
+    </dxf>
+    <dxf>
+      <font>
+        <b val="0"/>
+        <i val="0"/>
+        <strike val="0"/>
+        <condense val="0"/>
+        <extend val="0"/>
+        <outline val="0"/>
+        <shadow val="0"/>
+        <u val="none"/>
+        <vertAlign val="baseline"/>
+        <sz val="11"/>
+        <color indexed="8"/>
+        <name val="Calibri"/>
+        <family val="2"/>
+        <scheme val="none"/>
+      </font>
+      <numFmt numFmtId="0" formatCode="General"/>
+      <fill>
+        <patternFill patternType="none">
+          <fgColor indexed="64"/>
+          <bgColor indexed="65"/>
+        </patternFill>
+      </fill>
+      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="0" indent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
+      <protection locked="1" hidden="0"/>
+    </dxf>
+    <dxf>
+      <font>
+        <b val="0"/>
+        <i val="0"/>
+        <strike val="0"/>
+        <condense val="0"/>
+        <extend val="0"/>
+        <outline val="0"/>
+        <shadow val="0"/>
+        <u val="none"/>
+        <vertAlign val="baseline"/>
+        <sz val="11"/>
+        <color indexed="8"/>
+        <name val="Calibri"/>
+        <family val="2"/>
+        <scheme val="none"/>
+      </font>
+      <numFmt numFmtId="0" formatCode="General"/>
+      <fill>
+        <patternFill patternType="none">
+          <fgColor indexed="64"/>
+          <bgColor indexed="65"/>
+        </patternFill>
+      </fill>
+      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="0" indent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
+      <protection locked="1" hidden="0"/>
+    </dxf>
+    <dxf>
+      <font>
+        <b val="0"/>
+        <i val="0"/>
+        <strike val="0"/>
+        <condense val="0"/>
+        <extend val="0"/>
+        <outline val="0"/>
+        <shadow val="0"/>
+        <u val="none"/>
+        <vertAlign val="baseline"/>
+        <sz val="11"/>
+        <color indexed="8"/>
+        <name val="Calibri"/>
+        <family val="2"/>
+        <scheme val="none"/>
+      </font>
+      <numFmt numFmtId="0" formatCode="General"/>
+      <fill>
+        <patternFill patternType="none">
+          <fgColor indexed="64"/>
+          <bgColor indexed="65"/>
+        </patternFill>
+      </fill>
+      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="0" indent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
+      <protection locked="1" hidden="0"/>
+    </dxf>
+    <dxf>
+      <font>
+        <b val="0"/>
+        <i val="0"/>
+        <strike val="0"/>
+        <condense val="0"/>
+        <extend val="0"/>
+        <outline val="0"/>
+        <shadow val="0"/>
+        <u val="none"/>
+        <vertAlign val="baseline"/>
+        <sz val="11"/>
+        <color indexed="8"/>
+        <name val="Calibri"/>
+        <family val="2"/>
+        <scheme val="none"/>
+      </font>
+      <numFmt numFmtId="0" formatCode="General"/>
+      <fill>
+        <patternFill patternType="none">
+          <fgColor indexed="64"/>
+          <bgColor indexed="65"/>
+        </patternFill>
+      </fill>
+      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="0" indent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
+      <protection locked="1" hidden="0"/>
+    </dxf>
+    <dxf>
+      <font>
+        <b val="0"/>
+        <i val="0"/>
+        <strike val="0"/>
+        <condense val="0"/>
+        <extend val="0"/>
+        <outline val="0"/>
+        <shadow val="0"/>
+        <u val="none"/>
+        <vertAlign val="baseline"/>
+        <sz val="11"/>
+        <color indexed="8"/>
+        <name val="Calibri"/>
+        <family val="2"/>
+        <scheme val="none"/>
+      </font>
+      <numFmt numFmtId="0" formatCode="General"/>
+      <fill>
+        <patternFill patternType="none">
+          <fgColor indexed="64"/>
+          <bgColor indexed="65"/>
+        </patternFill>
+      </fill>
+      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="0" indent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
+      <protection locked="1" hidden="0"/>
+    </dxf>
+    <dxf>
+      <font>
+        <b val="0"/>
+        <i val="0"/>
+        <strike val="0"/>
+        <condense val="0"/>
+        <extend val="0"/>
+        <outline val="0"/>
+        <shadow val="0"/>
+        <u val="none"/>
+        <vertAlign val="baseline"/>
+        <sz val="11"/>
+        <color indexed="8"/>
+        <name val="Calibri"/>
+        <family val="2"/>
+        <scheme val="none"/>
+      </font>
+      <numFmt numFmtId="0" formatCode="General"/>
+      <fill>
+        <patternFill patternType="none">
+          <fgColor indexed="64"/>
+          <bgColor indexed="65"/>
+        </patternFill>
+      </fill>
+      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="0" indent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
+      <protection locked="1" hidden="0"/>
+    </dxf>
+    <dxf>
+      <font>
+        <b val="0"/>
+        <i val="0"/>
+        <strike val="0"/>
+        <condense val="0"/>
+        <extend val="0"/>
+        <outline val="0"/>
+        <shadow val="0"/>
+        <u val="none"/>
+        <vertAlign val="baseline"/>
+        <sz val="11"/>
+        <color indexed="8"/>
+        <name val="Calibri"/>
+        <family val="2"/>
+        <scheme val="none"/>
+      </font>
+      <numFmt numFmtId="0" formatCode="General"/>
+      <fill>
+        <patternFill patternType="none">
+          <fgColor indexed="64"/>
+          <bgColor indexed="65"/>
+        </patternFill>
+      </fill>
+      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="0" indent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
+      <protection locked="1" hidden="0"/>
+    </dxf>
+    <dxf>
+      <font>
+        <b val="0"/>
+        <i val="0"/>
+        <strike val="0"/>
+        <condense val="0"/>
+        <extend val="0"/>
+        <outline val="0"/>
+        <shadow val="0"/>
+        <u val="none"/>
+        <vertAlign val="baseline"/>
+        <sz val="11"/>
+        <color indexed="8"/>
+        <name val="Calibri"/>
+        <family val="2"/>
+        <scheme val="none"/>
+      </font>
+      <numFmt numFmtId="0" formatCode="General"/>
+      <fill>
+        <patternFill patternType="none">
+          <fgColor indexed="64"/>
+          <bgColor indexed="65"/>
+        </patternFill>
+      </fill>
+      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="0" indent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
+      <protection locked="1" hidden="0"/>
+    </dxf>
+    <dxf>
+      <font>
+        <b val="0"/>
+        <i val="0"/>
+        <strike val="0"/>
+        <condense val="0"/>
+        <extend val="0"/>
+        <outline val="0"/>
+        <shadow val="0"/>
+        <u val="none"/>
+        <vertAlign val="baseline"/>
+        <sz val="11"/>
+        <color indexed="8"/>
+        <name val="Calibri"/>
+        <family val="2"/>
+        <scheme val="none"/>
+      </font>
+      <numFmt numFmtId="0" formatCode="General"/>
+      <fill>
+        <patternFill patternType="none">
+          <fgColor indexed="64"/>
+          <bgColor indexed="65"/>
+        </patternFill>
+      </fill>
+      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="0" indent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
+      <protection locked="1" hidden="0"/>
+    </dxf>
+    <dxf>
+      <font>
+        <b val="0"/>
+        <i val="0"/>
+        <strike val="0"/>
+        <condense val="0"/>
+        <extend val="0"/>
+        <outline val="0"/>
+        <shadow val="0"/>
+        <u val="none"/>
+        <vertAlign val="baseline"/>
+        <sz val="11"/>
+        <color indexed="8"/>
+        <name val="Calibri"/>
+        <family val="2"/>
+        <scheme val="none"/>
+      </font>
+      <numFmt numFmtId="0" formatCode="General"/>
+      <fill>
+        <patternFill patternType="none">
+          <fgColor indexed="64"/>
+          <bgColor indexed="65"/>
+        </patternFill>
+      </fill>
+      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="0" indent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
+      <protection locked="1" hidden="0"/>
+    </dxf>
+    <dxf>
+      <font>
+        <b val="0"/>
+        <i val="0"/>
+        <strike val="0"/>
+        <condense val="0"/>
+        <extend val="0"/>
+        <outline val="0"/>
+        <shadow val="0"/>
+        <u val="none"/>
+        <vertAlign val="baseline"/>
+        <sz val="11"/>
+        <color indexed="8"/>
+        <name val="Calibri"/>
+        <family val="2"/>
+        <scheme val="none"/>
+      </font>
+      <numFmt numFmtId="0" formatCode="General"/>
+      <fill>
+        <patternFill patternType="none">
+          <fgColor indexed="64"/>
+          <bgColor indexed="65"/>
+        </patternFill>
+      </fill>
+      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="0" indent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
+      <protection locked="1" hidden="0"/>
+    </dxf>
+    <dxf>
+      <font>
+        <b val="0"/>
+        <i val="0"/>
+        <strike val="0"/>
+        <condense val="0"/>
+        <extend val="0"/>
+        <outline val="0"/>
+        <shadow val="0"/>
+        <u val="none"/>
+        <vertAlign val="baseline"/>
+        <sz val="11"/>
+        <color indexed="8"/>
+        <name val="Calibri"/>
+        <family val="2"/>
+        <scheme val="none"/>
+      </font>
+      <numFmt numFmtId="0" formatCode="General"/>
+      <fill>
+        <patternFill patternType="none">
+          <fgColor indexed="64"/>
+          <bgColor indexed="65"/>
+        </patternFill>
+      </fill>
+      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="0" indent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
+      <protection locked="1" hidden="0"/>
+    </dxf>
+    <dxf>
+      <font>
+        <b val="0"/>
+        <i val="0"/>
+        <strike val="0"/>
+        <condense val="0"/>
+        <extend val="0"/>
+        <outline val="0"/>
+        <shadow val="0"/>
+        <u val="none"/>
+        <vertAlign val="baseline"/>
+        <sz val="11"/>
+        <color indexed="8"/>
+        <name val="Calibri"/>
+        <family val="2"/>
+        <scheme val="none"/>
+      </font>
+      <numFmt numFmtId="0" formatCode="General"/>
+      <fill>
+        <patternFill patternType="none">
+          <fgColor indexed="64"/>
+          <bgColor indexed="65"/>
+        </patternFill>
+      </fill>
+      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="0" indent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
+      <protection locked="1" hidden="0"/>
+    </dxf>
+    <dxf>
+      <font>
+        <b val="0"/>
+        <i val="0"/>
+        <strike val="0"/>
+        <condense val="0"/>
+        <extend val="0"/>
+        <outline val="0"/>
+        <shadow val="0"/>
+        <u val="none"/>
+        <vertAlign val="baseline"/>
+        <sz val="11"/>
+        <color indexed="8"/>
+        <name val="Calibri"/>
+        <family val="2"/>
+        <scheme val="none"/>
+      </font>
+      <numFmt numFmtId="0" formatCode="General"/>
+      <fill>
+        <patternFill patternType="none">
+          <fgColor indexed="64"/>
+          <bgColor indexed="65"/>
+        </patternFill>
+      </fill>
+      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="0" indent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
+      <protection locked="1" hidden="0"/>
+    </dxf>
+  </dxfs>
   <tableStyles count="0" defaultTableStyle="TableStyleMedium2" defaultPivotStyle="PivotStyleLight16"/>
   <extLst>
     <ext xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" uri="{EB79DEF2-80B8-43e5-95BD-54CBDDF9020C}">
@@ -66,6 +2712,131 @@
     </ext>
   </extLst>
 </styleSheet>
+</file>
+
+<file path=xl/tables/table1.xml><?xml version="1.0" encoding="utf-8"?>
+<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="xr xr3" id="1" xr:uid="{ABF1633A-4477-4CB2-96F3-9AE941D92E43}" name="Tableau1" displayName="Tableau1" ref="A1:N7" totalsRowShown="0" headerRowDxfId="60" dataDxfId="61">
+  <autoFilter ref="A1:N7" xr:uid="{ABF1633A-4477-4CB2-96F3-9AE941D92E43}"/>
+  <tableColumns count="14">
+    <tableColumn id="1" xr3:uid="{8007380D-3CD0-49F7-B888-F883EAAAD348}" name="cr604_client_gpid" dataDxfId="75"/>
+    <tableColumn id="2" xr3:uid="{F336912B-4D63-45F6-A70C-E9A7369E2DFF}" name="createdon" dataDxfId="74"/>
+    <tableColumn id="3" xr3:uid="{72016A0C-F5B2-43F9-8E54-8B332DADF614}" name="cr604_cin" dataDxfId="73"/>
+    <tableColumn id="4" xr3:uid="{426680CC-F812-41D5-B56B-59352233538F}" name="cr604_name" dataDxfId="72"/>
+    <tableColumn id="5" xr3:uid="{6C7B37C6-78C1-4405-93A2-A791EAF8B579}" name="cr604_email" dataDxfId="71"/>
+    <tableColumn id="6" xr3:uid="{1E4F9A79-11FF-45CA-AB22-C8D3CA1B2AB9}" name="cr604_phone" dataDxfId="70"/>
+    <tableColumn id="7" xr3:uid="{C0C6EF2F-88E0-4A31-9663-D0D9BBC70281}" name="cr604_address" dataDxfId="69"/>
+    <tableColumn id="8" xr3:uid="{3ABC5801-5649-49EF-B765-6B0BAEADB8DF}" name="cr604_clienttype" dataDxfId="68"/>
+    <tableColumn id="9" xr3:uid="{C19612AA-FE1E-42E9-9D5D-67253B2F9318}" name="cr604_paymentmethod" dataDxfId="67"/>
+    <tableColumn id="10" xr3:uid="{C1097FAD-1843-4C77-B75D-F461B2B9750E}" name="cr604_currency" dataDxfId="66"/>
+    <tableColumn id="11" xr3:uid="{88E96DAB-E5C2-43D9-9775-DE3C9B60B1F5}" name="cr604_status" dataDxfId="65"/>
+    <tableColumn id="12" xr3:uid="{6CF98715-1908-4D3C-AE7D-46A00C59278C}" name="City" dataDxfId="64"/>
+    <tableColumn id="13" xr3:uid="{7BD6DBC0-26E4-4492-8E46-DDA356A02F8A}" name="Country" dataDxfId="63"/>
+    <tableColumn id="14" xr3:uid="{D464A5DF-ACFB-40D7-A01D-26E9D1E559C4}" name="IsActive" dataDxfId="62"/>
+  </tableColumns>
+  <tableStyleInfo name="TableStyleLight7" showFirstColumn="0" showLastColumn="0" showRowStripes="1" showColumnStripes="0"/>
+</table>
+</file>
+
+<file path=xl/tables/table2.xml><?xml version="1.0" encoding="utf-8"?>
+<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="xr xr3" id="2" xr:uid="{CA0316EA-52DA-48F1-9066-22A4C325529A}" name="Tableau2" displayName="Tableau2" ref="A1:F3" totalsRowShown="0" headerRowDxfId="52" dataDxfId="53">
+  <autoFilter ref="A1:F3" xr:uid="{CA0316EA-52DA-48F1-9066-22A4C325529A}"/>
+  <tableColumns count="6">
+    <tableColumn id="1" xr3:uid="{415FF128-68E1-432C-ADA8-2A0879476029}" name="Expensefix_Id" dataDxfId="59"/>
+    <tableColumn id="2" xr3:uid="{23E93EB4-3154-418E-8865-1061D60345A4}" name="createdon" dataDxfId="58"/>
+    <tableColumn id="3" xr3:uid="{0D7AFC2A-7922-49D6-9358-CF9B56D307C6}" name="Expense_Name" dataDxfId="57"/>
+    <tableColumn id="4" xr3:uid="{BDDC8434-E4DB-4EFD-852A-79FB35C74D2E}" name="Expense_Type" dataDxfId="56"/>
+    <tableColumn id="5" xr3:uid="{CC752734-5DE7-494F-8375-4EAA6C990096}" name="Amount" dataDxfId="55"/>
+    <tableColumn id="6" xr3:uid="{859E37D1-CED4-4DE3-A485-136BA1779692}" name="Status" dataDxfId="54"/>
+  </tableColumns>
+  <tableStyleInfo name="TableStyleLight7" showFirstColumn="0" showLastColumn="0" showRowStripes="1" showColumnStripes="0"/>
+</table>
+</file>
+
+<file path=xl/tables/table3.xml><?xml version="1.0" encoding="utf-8"?>
+<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="xr xr3" id="3" xr:uid="{6914BDA8-228C-4485-9166-762CC62DB448}" name="Tableau3" displayName="Tableau3" ref="A1:J9" totalsRowShown="0" headerRowDxfId="40" dataDxfId="41">
+  <autoFilter ref="A1:J9" xr:uid="{6914BDA8-228C-4485-9166-762CC62DB448}"/>
+  <tableColumns count="10">
+    <tableColumn id="1" xr3:uid="{30F0F40D-1320-418B-8DB3-B33F1F63D883}" name="Expense_Result_Id" dataDxfId="51"/>
+    <tableColumn id="2" xr3:uid="{A8F9D97D-93DB-4C9D-9E24-39E137118398}" name="createdon" dataDxfId="50"/>
+    <tableColumn id="3" xr3:uid="{1E6E0627-525B-4679-BE86-022D1FB5E41F}" name="Expense_Name" dataDxfId="49"/>
+    <tableColumn id="4" xr3:uid="{40ED29CB-F33D-496B-8F65-04FF2B2A4D75}" name="Expense_Type" dataDxfId="48"/>
+    <tableColumn id="5" xr3:uid="{5964FA26-E095-43BA-B22B-1B9BFBBA3C8F}" name="Estimated_Amount" dataDxfId="47"/>
+    <tableColumn id="6" xr3:uid="{53B7FA2C-F03C-4AEB-8843-6AEDCECC1E0D}" name="Actual_Amount" dataDxfId="46"/>
+    <tableColumn id="7" xr3:uid="{767989E6-836C-429D-BB20-3EA5D08528FA}" name="Charge_Status" dataDxfId="45"/>
+    <tableColumn id="8" xr3:uid="{BCB3D146-B38B-4A45-BF39-B01E68BC296F}" name="Covred_Day" dataDxfId="44"/>
+    <tableColumn id="9" xr3:uid="{262AA35D-E3C9-4211-80C8-29DA752620A7}" name="Month" dataDxfId="43"/>
+    <tableColumn id="10" xr3:uid="{0B81C404-5C4E-484A-AA6E-9DEC04F5DD63}" name="Year" dataDxfId="42"/>
+  </tableColumns>
+  <tableStyleInfo name="TableStyleLight7" showFirstColumn="0" showLastColumn="0" showRowStripes="1" showColumnStripes="0"/>
+</table>
+</file>
+
+<file path=xl/tables/table4.xml><?xml version="1.0" encoding="utf-8"?>
+<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="xr xr3" id="4" xr:uid="{EA6E28BB-F856-4B91-92E0-6B7F094EBDC6}" name="Tableau4" displayName="Tableau4" ref="A1:F11" totalsRowShown="0" headerRowDxfId="32" dataDxfId="33">
+  <autoFilter ref="A1:F11" xr:uid="{EA6E28BB-F856-4B91-92E0-6B7F094EBDC6}"/>
+  <tableColumns count="6">
+    <tableColumn id="1" xr3:uid="{341555F1-5CE3-4C06-B178-25315E203E7F}" name="Invoice_Id" dataDxfId="39"/>
+    <tableColumn id="2" xr3:uid="{67B6ACB9-F03C-4074-9930-C731B32ED1A2}" name="createdon" dataDxfId="38"/>
+    <tableColumn id="3" xr3:uid="{B5CB91F5-B2B5-4693-AAA8-5EEEC7533862}" name="Client_Name" dataDxfId="37"/>
+    <tableColumn id="4" xr3:uid="{3826B149-65B8-4AF5-93A4-371901805942}" name="Payed_Amount" dataDxfId="36"/>
+    <tableColumn id="5" xr3:uid="{1B98D176-B915-437B-BA5F-36FC76A1AF2D}" name="Peiment_Date" dataDxfId="35"/>
+    <tableColumn id="6" xr3:uid="{C8533C0D-0CB9-46F3-A8D9-3229B2405BDE}" name="Commentaire_Paiement" dataDxfId="34"/>
+  </tableColumns>
+  <tableStyleInfo name="TableStyleLight7" showFirstColumn="0" showLastColumn="0" showRowStripes="1" showColumnStripes="0"/>
+</table>
+</file>
+
+<file path=xl/tables/table5.xml><?xml version="1.0" encoding="utf-8"?>
+<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="xr xr3" id="5" xr:uid="{4CF3D069-4950-4CDC-B1A0-59D22D08CF36}" name="Tableau5" displayName="Tableau5" ref="A1:G12" totalsRowShown="0" headerRowDxfId="23" dataDxfId="24">
+  <autoFilter ref="A1:G12" xr:uid="{4CF3D069-4950-4CDC-B1A0-59D22D08CF36}"/>
+  <tableColumns count="7">
+    <tableColumn id="1" xr3:uid="{1C979BA1-4C32-42A6-B2D5-6EEF845F9BF2}" name="Revenue_Results_Id" dataDxfId="31"/>
+    <tableColumn id="2" xr3:uid="{F4F8F17F-15D9-4B1B-AF7D-EA0DA757CBD2}" name="createdon" dataDxfId="30"/>
+    <tableColumn id="3" xr3:uid="{E91696C9-CD5C-4A44-BFD3-859E60012FBC}" name="Year" dataDxfId="29"/>
+    <tableColumn id="4" xr3:uid="{57E7FF0D-2EAF-4E9E-8E53-946DD8A7D7B7}" name="Month" dataDxfId="28"/>
+    <tableColumn id="5" xr3:uid="{9AFAA844-7843-4AB3-9C4F-36AD92DBEB4A}" name="Client_Name" dataDxfId="27"/>
+    <tableColumn id="6" xr3:uid="{42D5308E-BAEF-458E-AB95-AED2AA71AB23}" name="Invoice_Number" dataDxfId="26"/>
+    <tableColumn id="7" xr3:uid="{B5D9695A-8934-4A61-B3C4-303CB87DFA30}" name="Total_Amount" dataDxfId="25"/>
+  </tableColumns>
+  <tableStyleInfo name="TableStyleLight7" showFirstColumn="0" showLastColumn="0" showRowStripes="1" showColumnStripes="0"/>
+</table>
+</file>
+
+<file path=xl/tables/table6.xml><?xml version="1.0" encoding="utf-8"?>
+<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="xr xr3" id="6" xr:uid="{11F4BBA4-F661-4A49-8A7D-294C9849B253}" name="Tableau6" displayName="Tableau6" ref="A1:J3" totalsRowShown="0" headerRowDxfId="11" dataDxfId="12">
+  <autoFilter ref="A1:J3" xr:uid="{11F4BBA4-F661-4A49-8A7D-294C9849B253}"/>
+  <tableColumns count="10">
+    <tableColumn id="1" xr3:uid="{FEBEA157-2D66-4B67-8E55-55EF8FF96FC4}" name="Monthly_Financial_Activities_Id" dataDxfId="22"/>
+    <tableColumn id="2" xr3:uid="{3DF74067-BA0C-431F-AE9C-0662141339EC}" name="createdon" dataDxfId="21"/>
+    <tableColumn id="3" xr3:uid="{6E0A2293-2BCD-4CB5-9B7E-CC030B6CD5FC}" name="Year" dataDxfId="20"/>
+    <tableColumn id="4" xr3:uid="{4FE2F7C4-56D1-4A6A-8C8A-5C103461978D}" name="Month" dataDxfId="19"/>
+    <tableColumn id="5" xr3:uid="{B7B0232E-FD62-4BB3-90F8-11B26D9B2977}" name="Bank_Fund" dataDxfId="18"/>
+    <tableColumn id="6" xr3:uid="{91F37486-C0C1-4BCB-B133-4FCD12A5E03E}" name="Total_Revenue" dataDxfId="17"/>
+    <tableColumn id="7" xr3:uid="{8C040718-5CE7-4BE3-9BA8-0D6E5799832B}" name="Total_Expenses" dataDxfId="16"/>
+    <tableColumn id="8" xr3:uid="{F50A2A9B-EB6C-4DBD-9F69-63DEB2E24E48}" name="Rest" dataDxfId="15"/>
+    <tableColumn id="9" xr3:uid="{DBB3D3F4-3E64-4493-B044-8042A2197A5F}" name="Global_Rest" dataDxfId="14"/>
+    <tableColumn id="10" xr3:uid="{337D8A9F-EA66-4631-A80F-50A1487A9B54}" name="Financial_Status" dataDxfId="13"/>
+  </tableColumns>
+  <tableStyleInfo name="TableStyleLight7" showFirstColumn="0" showLastColumn="0" showRowStripes="1" showColumnStripes="0"/>
+</table>
+</file>
+
+<file path=xl/tables/table7.xml><?xml version="1.0" encoding="utf-8"?>
+<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="xr xr3" id="7" xr:uid="{DCCC299D-F4A9-46D6-B99F-ECC9A1711F28}" name="Tableau7" displayName="Tableau7" ref="A1:I3" totalsRowShown="0" headerRowDxfId="0" dataDxfId="1">
+  <autoFilter ref="A1:I3" xr:uid="{DCCC299D-F4A9-46D6-B99F-ECC9A1711F28}"/>
+  <tableColumns count="9">
+    <tableColumn id="1" xr3:uid="{DF05FFBA-F7C4-438F-BD5A-60E2A58D28AB}" name="Annual_Financial_Activities_Id" dataDxfId="10"/>
+    <tableColumn id="2" xr3:uid="{2EC49EED-6BFE-487D-B086-BE0C3ED8A5CA}" name="createdon" dataDxfId="9"/>
+    <tableColumn id="3" xr3:uid="{C33CBC62-AB34-4666-B0F4-D0F9BB3BDE44}" name="Year" dataDxfId="8"/>
+    <tableColumn id="4" xr3:uid="{A1DCDD73-FC65-41A9-9C06-B97619796A51}" name="Bank_Fund" dataDxfId="7"/>
+    <tableColumn id="5" xr3:uid="{CA2B39FB-73C4-4602-81CE-C921850D8D10}" name="Total_Revenue" dataDxfId="6"/>
+    <tableColumn id="6" xr3:uid="{C44D3967-57CB-464E-9CE0-18CC589EA10B}" name="Total_Expenses" dataDxfId="5"/>
+    <tableColumn id="7" xr3:uid="{87E595C3-C8E3-4A47-B360-7605079A37ED}" name="Rest" dataDxfId="4"/>
+    <tableColumn id="8" xr3:uid="{CAA4491F-AB1A-430B-A1EE-32C3C52FCB5D}" name="Global_Rest" dataDxfId="3"/>
+    <tableColumn id="9" xr3:uid="{557B6184-F760-4D8F-B8A4-3FC0441C05F5}" name="Financial_Status" dataDxfId="2"/>
+  </tableColumns>
+  <tableStyleInfo name="TableStyleLight7" showFirstColumn="0" showLastColumn="0" showRowStripes="1" showColumnStripes="0"/>
+</table>
 </file>
 
 <file path=xl/theme/theme1.xml><?xml version="1.0" encoding="utf-8"?>
@@ -330,10 +3101,1496 @@
 </file>
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
-  <dimension ref="A1"/>
-  <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
-  <sheetData/>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0000-000000000000}">
+  <dimension ref="A1:N7"/>
+  <sheetFormatPr baseColWidth="10" defaultColWidth="8.88671875" defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
+  <cols>
+    <col min="1" max="1" width="22.88671875" customWidth="1"/>
+    <col min="2" max="2" width="19.21875" customWidth="1"/>
+    <col min="3" max="3" width="16" customWidth="1"/>
+    <col min="4" max="4" width="18.88671875" customWidth="1"/>
+    <col min="5" max="5" width="16.77734375" customWidth="1"/>
+    <col min="6" max="6" width="18" customWidth="1"/>
+    <col min="7" max="7" width="17.6640625" customWidth="1"/>
+    <col min="8" max="8" width="22.77734375" customWidth="1"/>
+    <col min="9" max="9" width="28" customWidth="1"/>
+    <col min="10" max="10" width="22.21875" customWidth="1"/>
+    <col min="11" max="11" width="18.77734375" customWidth="1"/>
+    <col min="12" max="12" width="21.33203125" customWidth="1"/>
+    <col min="13" max="13" width="16.33203125" customWidth="1"/>
+    <col min="14" max="14" width="17.5546875" customWidth="1"/>
+  </cols>
+  <sheetData>
+    <row r="1" spans="1:14" x14ac:dyDescent="0.3">
+      <c r="A1" s="1" t="s">
+        <v>0</v>
+      </c>
+      <c r="B1" s="1" t="s">
+        <v>1</v>
+      </c>
+      <c r="C1" s="1" t="s">
+        <v>2</v>
+      </c>
+      <c r="D1" s="1" t="s">
+        <v>3</v>
+      </c>
+      <c r="E1" s="1" t="s">
+        <v>4</v>
+      </c>
+      <c r="F1" s="1" t="s">
+        <v>5</v>
+      </c>
+      <c r="G1" s="1" t="s">
+        <v>6</v>
+      </c>
+      <c r="H1" s="1" t="s">
+        <v>7</v>
+      </c>
+      <c r="I1" s="1" t="s">
+        <v>8</v>
+      </c>
+      <c r="J1" s="1" t="s">
+        <v>9</v>
+      </c>
+      <c r="K1" s="1" t="s">
+        <v>10</v>
+      </c>
+      <c r="L1" s="1" t="s">
+        <v>11</v>
+      </c>
+      <c r="M1" s="1" t="s">
+        <v>12</v>
+      </c>
+      <c r="N1" s="1" t="s">
+        <v>13</v>
+      </c>
+    </row>
+    <row r="2" spans="1:14" x14ac:dyDescent="0.3">
+      <c r="A2" s="1" t="s">
+        <v>14</v>
+      </c>
+      <c r="B2" s="1" t="s">
+        <v>15</v>
+      </c>
+      <c r="C2" s="1">
+        <v>7498188</v>
+      </c>
+      <c r="D2" s="1" t="s">
+        <v>16</v>
+      </c>
+      <c r="E2" s="1" t="s">
+        <v>17</v>
+      </c>
+      <c r="F2" s="1">
+        <v>23267646</v>
+      </c>
+      <c r="G2" s="1" t="s">
+        <v>18</v>
+      </c>
+      <c r="H2" s="1" t="s">
+        <v>19</v>
+      </c>
+      <c r="I2" s="1" t="s">
+        <v>20</v>
+      </c>
+      <c r="J2" s="1" t="s">
+        <v>21</v>
+      </c>
+      <c r="K2" s="1" t="s">
+        <v>22</v>
+      </c>
+      <c r="L2" s="1" t="s">
+        <v>23</v>
+      </c>
+      <c r="M2" s="1" t="s">
+        <v>24</v>
+      </c>
+      <c r="N2" s="1" t="s">
+        <v>25</v>
+      </c>
+    </row>
+    <row r="3" spans="1:14" x14ac:dyDescent="0.3">
+      <c r="A3" s="1" t="s">
+        <v>26</v>
+      </c>
+      <c r="B3" s="1" t="s">
+        <v>27</v>
+      </c>
+      <c r="C3" s="1">
+        <v>7896522</v>
+      </c>
+      <c r="D3" s="1" t="s">
+        <v>28</v>
+      </c>
+      <c r="E3" s="1" t="s">
+        <v>29</v>
+      </c>
+      <c r="F3" s="1">
+        <v>99854632</v>
+      </c>
+      <c r="G3" s="1" t="s">
+        <v>30</v>
+      </c>
+      <c r="H3" s="1" t="s">
+        <v>31</v>
+      </c>
+      <c r="I3" s="1" t="s">
+        <v>32</v>
+      </c>
+      <c r="J3" s="1" t="s">
+        <v>33</v>
+      </c>
+      <c r="K3" s="1" t="s">
+        <v>34</v>
+      </c>
+      <c r="L3" s="1" t="s">
+        <v>35</v>
+      </c>
+      <c r="M3" s="1" t="s">
+        <v>36</v>
+      </c>
+      <c r="N3" s="1" t="s">
+        <v>37</v>
+      </c>
+    </row>
+    <row r="4" spans="1:14" x14ac:dyDescent="0.3">
+      <c r="A4" s="1" t="s">
+        <v>38</v>
+      </c>
+      <c r="B4" s="1" t="s">
+        <v>39</v>
+      </c>
+      <c r="C4" s="1">
+        <v>79856123</v>
+      </c>
+      <c r="D4" s="1" t="s">
+        <v>40</v>
+      </c>
+      <c r="E4" s="1" t="s">
+        <v>41</v>
+      </c>
+      <c r="F4" s="1">
+        <v>23658974</v>
+      </c>
+      <c r="G4" s="1" t="s">
+        <v>18</v>
+      </c>
+      <c r="H4" s="1" t="s">
+        <v>31</v>
+      </c>
+      <c r="I4" s="1" t="s">
+        <v>42</v>
+      </c>
+      <c r="J4" s="1" t="s">
+        <v>43</v>
+      </c>
+      <c r="K4" s="1" t="s">
+        <v>34</v>
+      </c>
+      <c r="L4" s="1" t="s">
+        <v>23</v>
+      </c>
+      <c r="M4" s="1" t="s">
+        <v>24</v>
+      </c>
+      <c r="N4" s="1" t="s">
+        <v>37</v>
+      </c>
+    </row>
+    <row r="5" spans="1:14" x14ac:dyDescent="0.3">
+      <c r="A5" s="1" t="s">
+        <v>44</v>
+      </c>
+      <c r="B5" s="1" t="s">
+        <v>45</v>
+      </c>
+      <c r="C5" s="1">
+        <v>78965412</v>
+      </c>
+      <c r="D5" s="1" t="s">
+        <v>46</v>
+      </c>
+      <c r="E5" s="1" t="s">
+        <v>47</v>
+      </c>
+      <c r="F5" s="1">
+        <v>23547891</v>
+      </c>
+      <c r="G5" s="1" t="s">
+        <v>48</v>
+      </c>
+      <c r="H5" s="1" t="s">
+        <v>19</v>
+      </c>
+      <c r="I5" s="1" t="s">
+        <v>32</v>
+      </c>
+      <c r="J5" s="1" t="s">
+        <v>33</v>
+      </c>
+      <c r="K5" s="1" t="s">
+        <v>34</v>
+      </c>
+      <c r="L5" s="1" t="s">
+        <v>49</v>
+      </c>
+      <c r="M5" s="1" t="s">
+        <v>24</v>
+      </c>
+      <c r="N5" s="1" t="s">
+        <v>37</v>
+      </c>
+    </row>
+    <row r="6" spans="1:14" x14ac:dyDescent="0.3">
+      <c r="A6" s="1" t="s">
+        <v>50</v>
+      </c>
+      <c r="B6" s="1" t="s">
+        <v>51</v>
+      </c>
+      <c r="C6" s="1">
+        <v>6325411</v>
+      </c>
+      <c r="D6" s="1" t="s">
+        <v>52</v>
+      </c>
+      <c r="E6" s="1" t="s">
+        <v>53</v>
+      </c>
+      <c r="F6" s="1">
+        <v>23658971</v>
+      </c>
+      <c r="G6" s="1" t="s">
+        <v>54</v>
+      </c>
+      <c r="H6" s="1" t="s">
+        <v>31</v>
+      </c>
+      <c r="I6" s="1" t="s">
+        <v>32</v>
+      </c>
+      <c r="J6" s="1" t="s">
+        <v>33</v>
+      </c>
+      <c r="K6" s="1" t="s">
+        <v>22</v>
+      </c>
+      <c r="L6" s="1" t="s">
+        <v>55</v>
+      </c>
+      <c r="M6" s="1" t="s">
+        <v>24</v>
+      </c>
+      <c r="N6" s="1" t="s">
+        <v>25</v>
+      </c>
+    </row>
+    <row r="7" spans="1:14" x14ac:dyDescent="0.3">
+      <c r="A7" s="1" t="s">
+        <v>56</v>
+      </c>
+      <c r="B7" s="1" t="s">
+        <v>57</v>
+      </c>
+      <c r="C7" s="1">
+        <v>5897466</v>
+      </c>
+      <c r="D7" s="1" t="s">
+        <v>58</v>
+      </c>
+      <c r="E7" s="1" t="s">
+        <v>59</v>
+      </c>
+      <c r="F7" s="1">
+        <v>20236874</v>
+      </c>
+      <c r="G7" s="1" t="s">
+        <v>30</v>
+      </c>
+      <c r="H7" s="1" t="s">
+        <v>31</v>
+      </c>
+      <c r="I7" s="1" t="s">
+        <v>20</v>
+      </c>
+      <c r="J7" s="1" t="s">
+        <v>43</v>
+      </c>
+      <c r="K7" s="1" t="s">
+        <v>34</v>
+      </c>
+      <c r="L7" s="1" t="s">
+        <v>35</v>
+      </c>
+      <c r="M7" s="1" t="s">
+        <v>36</v>
+      </c>
+      <c r="N7" s="1" t="s">
+        <v>37</v>
+      </c>
+    </row>
+  </sheetData>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
+  <tableParts count="1">
+    <tablePart r:id="rId1"/>
+  </tableParts>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{D9687597-F176-4C01-96D6-C27379F0A102}">
+  <dimension ref="A1:F3"/>
+  <sheetFormatPr baseColWidth="10" defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
+  <cols>
+    <col min="1" max="1" width="16.77734375" customWidth="1"/>
+    <col min="2" max="2" width="19.21875" customWidth="1"/>
+    <col min="3" max="3" width="24.77734375" customWidth="1"/>
+    <col min="4" max="4" width="17.44140625" customWidth="1"/>
+    <col min="5" max="5" width="14.44140625" customWidth="1"/>
+    <col min="6" max="6" width="14.77734375" customWidth="1"/>
+  </cols>
+  <sheetData>
+    <row r="1" spans="1:6" x14ac:dyDescent="0.3">
+      <c r="A1" s="1" t="s">
+        <v>60</v>
+      </c>
+      <c r="B1" s="1" t="s">
+        <v>1</v>
+      </c>
+      <c r="C1" s="1" t="s">
+        <v>61</v>
+      </c>
+      <c r="D1" s="1" t="s">
+        <v>62</v>
+      </c>
+      <c r="E1" s="1" t="s">
+        <v>63</v>
+      </c>
+      <c r="F1" s="1" t="s">
+        <v>64</v>
+      </c>
+    </row>
+    <row r="2" spans="1:6" x14ac:dyDescent="0.3">
+      <c r="A2" s="1" t="s">
+        <v>65</v>
+      </c>
+      <c r="B2" s="1" t="s">
+        <v>66</v>
+      </c>
+      <c r="C2" s="1" t="s">
+        <v>67</v>
+      </c>
+      <c r="D2" s="1" t="s">
+        <v>68</v>
+      </c>
+      <c r="E2" s="1">
+        <v>2500</v>
+      </c>
+      <c r="F2" s="1" t="s">
+        <v>69</v>
+      </c>
+    </row>
+    <row r="3" spans="1:6" x14ac:dyDescent="0.3">
+      <c r="A3" s="1" t="s">
+        <v>70</v>
+      </c>
+      <c r="B3" s="1" t="s">
+        <v>71</v>
+      </c>
+      <c r="C3" s="1" t="s">
+        <v>72</v>
+      </c>
+      <c r="D3" s="1" t="s">
+        <v>73</v>
+      </c>
+      <c r="E3" s="1">
+        <v>1200</v>
+      </c>
+      <c r="F3" s="1" t="s">
+        <v>69</v>
+      </c>
+    </row>
+  </sheetData>
+  <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
+  <tableParts count="1">
+    <tablePart r:id="rId1"/>
+  </tableParts>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet3.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{B55D414D-1A21-46BF-B15F-22A67601AE5A}">
+  <dimension ref="A1:J9"/>
+  <sheetFormatPr baseColWidth="10" defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
+  <cols>
+    <col min="1" max="1" width="25.88671875" customWidth="1"/>
+    <col min="2" max="2" width="17.5546875" customWidth="1"/>
+    <col min="3" max="3" width="24.33203125" customWidth="1"/>
+    <col min="4" max="4" width="20" customWidth="1"/>
+    <col min="5" max="5" width="22.33203125" customWidth="1"/>
+    <col min="6" max="6" width="21.44140625" customWidth="1"/>
+    <col min="7" max="7" width="19" customWidth="1"/>
+    <col min="8" max="8" width="18.5546875" customWidth="1"/>
+    <col min="10" max="10" width="15.88671875" customWidth="1"/>
+  </cols>
+  <sheetData>
+    <row r="1" spans="1:10" x14ac:dyDescent="0.3">
+      <c r="A1" s="1" t="s">
+        <v>74</v>
+      </c>
+      <c r="B1" s="1" t="s">
+        <v>1</v>
+      </c>
+      <c r="C1" s="1" t="s">
+        <v>61</v>
+      </c>
+      <c r="D1" s="1" t="s">
+        <v>62</v>
+      </c>
+      <c r="E1" s="1" t="s">
+        <v>75</v>
+      </c>
+      <c r="F1" s="1" t="s">
+        <v>76</v>
+      </c>
+      <c r="G1" s="1" t="s">
+        <v>77</v>
+      </c>
+      <c r="H1" s="1" t="s">
+        <v>78</v>
+      </c>
+      <c r="I1" s="1" t="s">
+        <v>79</v>
+      </c>
+      <c r="J1" s="1" t="s">
+        <v>80</v>
+      </c>
+    </row>
+    <row r="2" spans="1:10" x14ac:dyDescent="0.3">
+      <c r="A2" s="1" t="s">
+        <v>81</v>
+      </c>
+      <c r="B2" s="1" t="s">
+        <v>82</v>
+      </c>
+      <c r="C2" s="1" t="s">
+        <v>83</v>
+      </c>
+      <c r="D2" s="1" t="s">
+        <v>84</v>
+      </c>
+      <c r="E2" s="1">
+        <v>2500</v>
+      </c>
+      <c r="F2" s="1">
+        <v>2500</v>
+      </c>
+      <c r="G2" s="1" t="s">
+        <v>85</v>
+      </c>
+      <c r="H2" s="1" t="s">
+        <v>86</v>
+      </c>
+      <c r="I2" s="1" t="s">
+        <v>87</v>
+      </c>
+      <c r="J2" s="1" t="s">
+        <v>88</v>
+      </c>
+    </row>
+    <row r="3" spans="1:10" x14ac:dyDescent="0.3">
+      <c r="A3" s="1" t="s">
+        <v>89</v>
+      </c>
+      <c r="B3" s="1" t="s">
+        <v>82</v>
+      </c>
+      <c r="C3" s="1" t="s">
+        <v>90</v>
+      </c>
+      <c r="D3" s="1" t="s">
+        <v>84</v>
+      </c>
+      <c r="E3" s="1">
+        <v>1000</v>
+      </c>
+      <c r="F3" s="1">
+        <v>1000</v>
+      </c>
+      <c r="G3" s="1" t="s">
+        <v>85</v>
+      </c>
+      <c r="H3" s="1" t="s">
+        <v>91</v>
+      </c>
+      <c r="I3" s="1" t="s">
+        <v>87</v>
+      </c>
+      <c r="J3" s="1" t="s">
+        <v>88</v>
+      </c>
+    </row>
+    <row r="4" spans="1:10" x14ac:dyDescent="0.3">
+      <c r="A4" s="1" t="s">
+        <v>92</v>
+      </c>
+      <c r="B4" s="1" t="s">
+        <v>93</v>
+      </c>
+      <c r="C4" s="1" t="s">
+        <v>83</v>
+      </c>
+      <c r="D4" s="1" t="s">
+        <v>84</v>
+      </c>
+      <c r="E4" s="1">
+        <v>2500</v>
+      </c>
+      <c r="F4" s="1">
+        <v>2500</v>
+      </c>
+      <c r="G4" s="1" t="s">
+        <v>85</v>
+      </c>
+      <c r="H4" s="1" t="s">
+        <v>94</v>
+      </c>
+      <c r="I4" s="1" t="s">
+        <v>87</v>
+      </c>
+      <c r="J4" s="1" t="s">
+        <v>95</v>
+      </c>
+    </row>
+    <row r="5" spans="1:10" x14ac:dyDescent="0.3">
+      <c r="A5" s="1" t="s">
+        <v>96</v>
+      </c>
+      <c r="B5" s="1" t="s">
+        <v>93</v>
+      </c>
+      <c r="C5" s="1" t="s">
+        <v>97</v>
+      </c>
+      <c r="D5" s="1" t="s">
+        <v>68</v>
+      </c>
+      <c r="E5" s="1">
+        <v>3000</v>
+      </c>
+      <c r="F5" s="1">
+        <v>3000</v>
+      </c>
+      <c r="G5" s="1" t="s">
+        <v>85</v>
+      </c>
+      <c r="H5" s="1" t="s">
+        <v>98</v>
+      </c>
+      <c r="I5" s="1" t="s">
+        <v>87</v>
+      </c>
+      <c r="J5" s="1" t="s">
+        <v>95</v>
+      </c>
+    </row>
+    <row r="6" spans="1:10" x14ac:dyDescent="0.3">
+      <c r="A6" s="1" t="s">
+        <v>99</v>
+      </c>
+      <c r="B6" s="1" t="s">
+        <v>93</v>
+      </c>
+      <c r="C6" s="1" t="s">
+        <v>90</v>
+      </c>
+      <c r="D6" s="1" t="s">
+        <v>84</v>
+      </c>
+      <c r="E6" s="1">
+        <v>1250</v>
+      </c>
+      <c r="F6" s="1">
+        <v>5000</v>
+      </c>
+      <c r="G6" s="1" t="s">
+        <v>100</v>
+      </c>
+      <c r="H6" s="1" t="s">
+        <v>101</v>
+      </c>
+      <c r="I6" s="1" t="s">
+        <v>87</v>
+      </c>
+      <c r="J6" s="1" t="s">
+        <v>95</v>
+      </c>
+    </row>
+    <row r="7" spans="1:10" x14ac:dyDescent="0.3">
+      <c r="A7" s="1" t="s">
+        <v>102</v>
+      </c>
+      <c r="B7" s="1" t="s">
+        <v>103</v>
+      </c>
+      <c r="C7" s="1" t="s">
+        <v>83</v>
+      </c>
+      <c r="D7" s="1" t="s">
+        <v>84</v>
+      </c>
+      <c r="E7" s="1">
+        <v>2500</v>
+      </c>
+      <c r="F7" s="1">
+        <v>2500</v>
+      </c>
+      <c r="G7" s="1" t="s">
+        <v>85</v>
+      </c>
+      <c r="H7" s="1" t="s">
+        <v>104</v>
+      </c>
+      <c r="I7" s="1" t="s">
+        <v>104</v>
+      </c>
+      <c r="J7" s="1" t="s">
+        <v>105</v>
+      </c>
+    </row>
+    <row r="8" spans="1:10" x14ac:dyDescent="0.3">
+      <c r="A8" s="1" t="s">
+        <v>106</v>
+      </c>
+      <c r="B8" s="1" t="s">
+        <v>103</v>
+      </c>
+      <c r="C8" s="1" t="s">
+        <v>90</v>
+      </c>
+      <c r="D8" s="1" t="s">
+        <v>84</v>
+      </c>
+      <c r="E8" s="1">
+        <v>2000</v>
+      </c>
+      <c r="F8" s="1">
+        <v>2000</v>
+      </c>
+      <c r="G8" s="1" t="s">
+        <v>85</v>
+      </c>
+      <c r="H8" s="1" t="s">
+        <v>86</v>
+      </c>
+      <c r="I8" s="1" t="s">
+        <v>104</v>
+      </c>
+      <c r="J8" s="1" t="s">
+        <v>105</v>
+      </c>
+    </row>
+    <row r="9" spans="1:10" x14ac:dyDescent="0.3">
+      <c r="A9" s="1" t="s">
+        <v>107</v>
+      </c>
+      <c r="B9" s="1" t="s">
+        <v>108</v>
+      </c>
+      <c r="C9" s="1" t="s">
+        <v>16</v>
+      </c>
+      <c r="D9" s="1" t="s">
+        <v>84</v>
+      </c>
+      <c r="E9" s="1">
+        <v>1000</v>
+      </c>
+      <c r="F9" s="1">
+        <v>1000</v>
+      </c>
+      <c r="G9" s="1" t="s">
+        <v>85</v>
+      </c>
+      <c r="H9" s="1" t="s">
+        <v>87</v>
+      </c>
+      <c r="I9" s="1" t="s">
+        <v>86</v>
+      </c>
+      <c r="J9" s="1" t="s">
+        <v>95</v>
+      </c>
+    </row>
+  </sheetData>
+  <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
+  <tableParts count="1">
+    <tablePart r:id="rId1"/>
+  </tableParts>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet4.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{31DB1A82-BF3D-48A6-A081-2BC8CB2C77CF}">
+  <dimension ref="A1:F11"/>
+  <sheetFormatPr baseColWidth="10" defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
+  <cols>
+    <col min="1" max="2" width="20.44140625" customWidth="1"/>
+    <col min="3" max="3" width="18.21875" customWidth="1"/>
+    <col min="4" max="4" width="22.5546875" customWidth="1"/>
+    <col min="5" max="5" width="20.5546875" customWidth="1"/>
+    <col min="6" max="6" width="31.21875" customWidth="1"/>
+  </cols>
+  <sheetData>
+    <row r="1" spans="1:6" x14ac:dyDescent="0.3">
+      <c r="A1" s="1" t="s">
+        <v>109</v>
+      </c>
+      <c r="B1" s="1" t="s">
+        <v>1</v>
+      </c>
+      <c r="C1" s="1" t="s">
+        <v>110</v>
+      </c>
+      <c r="D1" s="1" t="s">
+        <v>111</v>
+      </c>
+      <c r="E1" s="1" t="s">
+        <v>112</v>
+      </c>
+      <c r="F1" s="1" t="s">
+        <v>113</v>
+      </c>
+    </row>
+    <row r="2" spans="1:6" x14ac:dyDescent="0.3">
+      <c r="A2" s="1" t="s">
+        <v>114</v>
+      </c>
+      <c r="B2" s="1" t="s">
+        <v>115</v>
+      </c>
+      <c r="C2" s="1" t="s">
+        <v>16</v>
+      </c>
+      <c r="D2" s="1">
+        <v>2500</v>
+      </c>
+      <c r="E2" s="1" t="s">
+        <v>116</v>
+      </c>
+      <c r="F2" s="1" t="s">
+        <v>117</v>
+      </c>
+    </row>
+    <row r="3" spans="1:6" x14ac:dyDescent="0.3">
+      <c r="A3" s="1" t="s">
+        <v>118</v>
+      </c>
+      <c r="B3" s="1" t="s">
+        <v>115</v>
+      </c>
+      <c r="C3" s="1" t="s">
+        <v>46</v>
+      </c>
+      <c r="D3" s="1">
+        <v>500</v>
+      </c>
+      <c r="E3" s="1" t="s">
+        <v>119</v>
+      </c>
+      <c r="F3" s="1" t="s">
+        <v>117</v>
+      </c>
+    </row>
+    <row r="4" spans="1:6" x14ac:dyDescent="0.3">
+      <c r="A4" s="1" t="s">
+        <v>120</v>
+      </c>
+      <c r="B4" s="1" t="s">
+        <v>115</v>
+      </c>
+      <c r="C4" s="1" t="s">
+        <v>28</v>
+      </c>
+      <c r="D4" s="1">
+        <v>1500</v>
+      </c>
+      <c r="E4" s="1" t="s">
+        <v>121</v>
+      </c>
+      <c r="F4" s="1" t="s">
+        <v>117</v>
+      </c>
+    </row>
+    <row r="5" spans="1:6" x14ac:dyDescent="0.3">
+      <c r="A5" s="1" t="s">
+        <v>122</v>
+      </c>
+      <c r="B5" s="1" t="s">
+        <v>115</v>
+      </c>
+      <c r="C5" s="1" t="s">
+        <v>40</v>
+      </c>
+      <c r="D5" s="1">
+        <v>6500</v>
+      </c>
+      <c r="E5" s="1" t="s">
+        <v>123</v>
+      </c>
+      <c r="F5" s="1" t="s">
+        <v>117</v>
+      </c>
+    </row>
+    <row r="6" spans="1:6" x14ac:dyDescent="0.3">
+      <c r="A6" s="1" t="s">
+        <v>124</v>
+      </c>
+      <c r="B6" s="1" t="s">
+        <v>115</v>
+      </c>
+      <c r="C6" s="1" t="s">
+        <v>52</v>
+      </c>
+      <c r="D6" s="1">
+        <v>10000</v>
+      </c>
+      <c r="E6" s="1" t="s">
+        <v>125</v>
+      </c>
+      <c r="F6" s="1" t="s">
+        <v>117</v>
+      </c>
+    </row>
+    <row r="7" spans="1:6" x14ac:dyDescent="0.3">
+      <c r="A7" s="1" t="s">
+        <v>126</v>
+      </c>
+      <c r="B7" s="1" t="s">
+        <v>127</v>
+      </c>
+      <c r="C7" s="1" t="s">
+        <v>128</v>
+      </c>
+      <c r="D7" s="1">
+        <v>2000</v>
+      </c>
+      <c r="E7" s="1" t="s">
+        <v>129</v>
+      </c>
+      <c r="F7" s="1" t="s">
+        <v>130</v>
+      </c>
+    </row>
+    <row r="8" spans="1:6" x14ac:dyDescent="0.3">
+      <c r="A8" s="1" t="s">
+        <v>131</v>
+      </c>
+      <c r="B8" s="1" t="s">
+        <v>132</v>
+      </c>
+      <c r="C8" s="1" t="s">
+        <v>133</v>
+      </c>
+      <c r="D8" s="1">
+        <v>1000</v>
+      </c>
+      <c r="E8" s="1" t="s">
+        <v>134</v>
+      </c>
+      <c r="F8" s="1" t="s">
+        <v>130</v>
+      </c>
+    </row>
+    <row r="9" spans="1:6" x14ac:dyDescent="0.3">
+      <c r="A9" s="1" t="s">
+        <v>135</v>
+      </c>
+      <c r="B9" s="1" t="s">
+        <v>136</v>
+      </c>
+      <c r="C9" s="1" t="s">
+        <v>28</v>
+      </c>
+      <c r="D9" s="1">
+        <v>1500</v>
+      </c>
+      <c r="E9" s="1" t="s">
+        <v>137</v>
+      </c>
+      <c r="F9" s="1" t="s">
+        <v>130</v>
+      </c>
+    </row>
+    <row r="10" spans="1:6" x14ac:dyDescent="0.3">
+      <c r="A10" s="1" t="s">
+        <v>138</v>
+      </c>
+      <c r="B10" s="1" t="s">
+        <v>136</v>
+      </c>
+      <c r="C10" s="1" t="s">
+        <v>16</v>
+      </c>
+      <c r="D10" s="1">
+        <v>1000</v>
+      </c>
+      <c r="E10" s="1" t="s">
+        <v>139</v>
+      </c>
+      <c r="F10" s="1" t="s">
+        <v>130</v>
+      </c>
+    </row>
+    <row r="11" spans="1:6" x14ac:dyDescent="0.3">
+      <c r="A11" s="1" t="s">
+        <v>140</v>
+      </c>
+      <c r="B11" s="1" t="s">
+        <v>136</v>
+      </c>
+      <c r="C11" s="1" t="s">
+        <v>40</v>
+      </c>
+      <c r="D11" s="1">
+        <v>2000</v>
+      </c>
+      <c r="E11" s="1" t="s">
+        <v>141</v>
+      </c>
+      <c r="F11" s="1" t="s">
+        <v>130</v>
+      </c>
+    </row>
+  </sheetData>
+  <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
+  <tableParts count="1">
+    <tablePart r:id="rId1"/>
+  </tableParts>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet5.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{2F5D3E2B-D157-43B0-B84E-65ABF386AA8B}">
+  <dimension ref="A1:G12"/>
+  <sheetFormatPr baseColWidth="10" defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
+  <cols>
+    <col min="1" max="1" width="38" customWidth="1"/>
+    <col min="2" max="2" width="22.33203125" customWidth="1"/>
+    <col min="3" max="3" width="21.21875" customWidth="1"/>
+    <col min="4" max="4" width="14.77734375" customWidth="1"/>
+    <col min="5" max="5" width="18.88671875" customWidth="1"/>
+    <col min="6" max="6" width="22.109375" customWidth="1"/>
+    <col min="7" max="7" width="21.109375" customWidth="1"/>
+  </cols>
+  <sheetData>
+    <row r="1" spans="1:7" x14ac:dyDescent="0.3">
+      <c r="A1" s="1" t="s">
+        <v>142</v>
+      </c>
+      <c r="B1" s="1" t="s">
+        <v>1</v>
+      </c>
+      <c r="C1" s="1" t="s">
+        <v>80</v>
+      </c>
+      <c r="D1" s="1" t="s">
+        <v>79</v>
+      </c>
+      <c r="E1" s="1" t="s">
+        <v>110</v>
+      </c>
+      <c r="F1" s="1" t="s">
+        <v>143</v>
+      </c>
+      <c r="G1" s="1" t="s">
+        <v>144</v>
+      </c>
+    </row>
+    <row r="2" spans="1:7" x14ac:dyDescent="0.3">
+      <c r="A2" s="1" t="s">
+        <v>145</v>
+      </c>
+      <c r="B2" s="1" t="s">
+        <v>115</v>
+      </c>
+      <c r="C2" s="1" t="s">
+        <v>88</v>
+      </c>
+      <c r="D2" s="1" t="s">
+        <v>146</v>
+      </c>
+      <c r="E2" s="1" t="s">
+        <v>147</v>
+      </c>
+      <c r="F2" s="1">
+        <v>1</v>
+      </c>
+      <c r="G2" s="1">
+        <v>2500</v>
+      </c>
+    </row>
+    <row r="3" spans="1:7" x14ac:dyDescent="0.3">
+      <c r="A3" s="1" t="s">
+        <v>148</v>
+      </c>
+      <c r="B3" s="1" t="s">
+        <v>115</v>
+      </c>
+      <c r="C3" s="1" t="s">
+        <v>88</v>
+      </c>
+      <c r="D3" s="1" t="s">
+        <v>146</v>
+      </c>
+      <c r="E3" s="1" t="s">
+        <v>149</v>
+      </c>
+      <c r="F3" s="1">
+        <v>1</v>
+      </c>
+      <c r="G3" s="1">
+        <v>1500</v>
+      </c>
+    </row>
+    <row r="4" spans="1:7" x14ac:dyDescent="0.3">
+      <c r="A4" s="1" t="s">
+        <v>150</v>
+      </c>
+      <c r="B4" s="1" t="s">
+        <v>115</v>
+      </c>
+      <c r="C4" s="1" t="s">
+        <v>88</v>
+      </c>
+      <c r="D4" s="1" t="s">
+        <v>146</v>
+      </c>
+      <c r="E4" s="1" t="s">
+        <v>151</v>
+      </c>
+      <c r="F4" s="1">
+        <v>1</v>
+      </c>
+      <c r="G4" s="1">
+        <v>500</v>
+      </c>
+    </row>
+    <row r="5" spans="1:7" x14ac:dyDescent="0.3">
+      <c r="A5" s="1" t="s">
+        <v>152</v>
+      </c>
+      <c r="B5" s="1" t="s">
+        <v>115</v>
+      </c>
+      <c r="C5" s="1" t="s">
+        <v>88</v>
+      </c>
+      <c r="D5" s="1" t="s">
+        <v>146</v>
+      </c>
+      <c r="E5" s="1" t="s">
+        <v>153</v>
+      </c>
+      <c r="F5" s="1">
+        <v>1</v>
+      </c>
+      <c r="G5" s="1">
+        <v>6500</v>
+      </c>
+    </row>
+    <row r="6" spans="1:7" x14ac:dyDescent="0.3">
+      <c r="A6" s="1" t="s">
+        <v>154</v>
+      </c>
+      <c r="B6" s="1" t="s">
+        <v>115</v>
+      </c>
+      <c r="C6" s="1" t="s">
+        <v>88</v>
+      </c>
+      <c r="D6" s="1" t="s">
+        <v>146</v>
+      </c>
+      <c r="E6" s="1" t="s">
+        <v>52</v>
+      </c>
+      <c r="F6" s="1">
+        <v>1</v>
+      </c>
+      <c r="G6" s="1">
+        <v>10000</v>
+      </c>
+    </row>
+    <row r="7" spans="1:7" x14ac:dyDescent="0.3">
+      <c r="A7" s="1" t="s">
+        <v>155</v>
+      </c>
+      <c r="B7" s="1" t="s">
+        <v>156</v>
+      </c>
+      <c r="C7" s="1" t="s">
+        <v>105</v>
+      </c>
+      <c r="D7" s="1" t="s">
+        <v>91</v>
+      </c>
+      <c r="E7" s="1" t="s">
+        <v>157</v>
+      </c>
+      <c r="F7" s="1">
+        <v>3</v>
+      </c>
+      <c r="G7" s="1">
+        <v>8500</v>
+      </c>
+    </row>
+    <row r="8" spans="1:7" x14ac:dyDescent="0.3">
+      <c r="A8" s="1" t="s">
+        <v>158</v>
+      </c>
+      <c r="B8" s="1" t="s">
+        <v>159</v>
+      </c>
+      <c r="C8" s="1" t="s">
+        <v>160</v>
+      </c>
+      <c r="D8" s="1" t="s">
+        <v>161</v>
+      </c>
+      <c r="E8" s="1" t="s">
+        <v>162</v>
+      </c>
+      <c r="F8" s="1">
+        <v>4</v>
+      </c>
+      <c r="G8" s="1">
+        <v>15000</v>
+      </c>
+    </row>
+    <row r="9" spans="1:7" x14ac:dyDescent="0.3">
+      <c r="A9" s="1" t="s">
+        <v>163</v>
+      </c>
+      <c r="B9" s="1" t="s">
+        <v>164</v>
+      </c>
+      <c r="C9" s="1" t="s">
+        <v>165</v>
+      </c>
+      <c r="D9" s="1" t="s">
+        <v>166</v>
+      </c>
+      <c r="E9" s="1" t="s">
+        <v>167</v>
+      </c>
+      <c r="F9" s="1">
+        <v>2</v>
+      </c>
+      <c r="G9" s="1">
+        <v>12000</v>
+      </c>
+    </row>
+    <row r="10" spans="1:7" x14ac:dyDescent="0.3">
+      <c r="A10" s="1" t="s">
+        <v>168</v>
+      </c>
+      <c r="B10" s="1" t="s">
+        <v>169</v>
+      </c>
+      <c r="C10" s="1" t="s">
+        <v>105</v>
+      </c>
+      <c r="D10" s="1" t="s">
+        <v>104</v>
+      </c>
+      <c r="E10" s="1" t="s">
+        <v>147</v>
+      </c>
+      <c r="F10" s="1">
+        <v>1</v>
+      </c>
+      <c r="G10" s="1">
+        <v>1000</v>
+      </c>
+    </row>
+    <row r="11" spans="1:7" x14ac:dyDescent="0.3">
+      <c r="A11" s="1" t="s">
+        <v>170</v>
+      </c>
+      <c r="B11" s="1" t="s">
+        <v>169</v>
+      </c>
+      <c r="C11" s="1" t="s">
+        <v>105</v>
+      </c>
+      <c r="D11" s="1" t="s">
+        <v>104</v>
+      </c>
+      <c r="E11" s="1" t="s">
+        <v>149</v>
+      </c>
+      <c r="F11" s="1">
+        <v>1</v>
+      </c>
+      <c r="G11" s="1">
+        <v>1500</v>
+      </c>
+    </row>
+    <row r="12" spans="1:7" x14ac:dyDescent="0.3">
+      <c r="A12" s="1" t="s">
+        <v>171</v>
+      </c>
+      <c r="B12" s="1" t="s">
+        <v>169</v>
+      </c>
+      <c r="C12" s="1" t="s">
+        <v>105</v>
+      </c>
+      <c r="D12" s="1" t="s">
+        <v>104</v>
+      </c>
+      <c r="E12" s="1" t="s">
+        <v>153</v>
+      </c>
+      <c r="F12" s="1">
+        <v>1</v>
+      </c>
+      <c r="G12" s="1">
+        <v>2000</v>
+      </c>
+    </row>
+  </sheetData>
+  <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
+  <tableParts count="1">
+    <tablePart r:id="rId1"/>
+  </tableParts>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet6.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{A545285D-11C7-4A87-952E-30D58C5FAD89}">
+  <dimension ref="A1:J3"/>
+  <sheetFormatPr baseColWidth="10" defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
+  <cols>
+    <col min="1" max="1" width="37.6640625" customWidth="1"/>
+    <col min="2" max="2" width="18.77734375" customWidth="1"/>
+    <col min="5" max="5" width="24.109375" customWidth="1"/>
+    <col min="6" max="6" width="22" customWidth="1"/>
+    <col min="7" max="7" width="23" customWidth="1"/>
+    <col min="9" max="9" width="19.109375" customWidth="1"/>
+    <col min="10" max="10" width="24" customWidth="1"/>
+  </cols>
+  <sheetData>
+    <row r="1" spans="1:10" x14ac:dyDescent="0.3">
+      <c r="A1" s="1" t="s">
+        <v>172</v>
+      </c>
+      <c r="B1" s="1" t="s">
+        <v>1</v>
+      </c>
+      <c r="C1" s="1" t="s">
+        <v>80</v>
+      </c>
+      <c r="D1" s="1" t="s">
+        <v>79</v>
+      </c>
+      <c r="E1" s="1" t="s">
+        <v>173</v>
+      </c>
+      <c r="F1" s="1" t="s">
+        <v>174</v>
+      </c>
+      <c r="G1" s="1" t="s">
+        <v>175</v>
+      </c>
+      <c r="H1" s="1" t="s">
+        <v>176</v>
+      </c>
+      <c r="I1" s="1" t="s">
+        <v>177</v>
+      </c>
+      <c r="J1" s="1" t="s">
+        <v>178</v>
+      </c>
+    </row>
+    <row r="2" spans="1:10" x14ac:dyDescent="0.3">
+      <c r="A2" s="1" t="s">
+        <v>179</v>
+      </c>
+      <c r="B2" s="1" t="s">
+        <v>180</v>
+      </c>
+      <c r="C2" s="1" t="s">
+        <v>95</v>
+      </c>
+      <c r="D2" s="1" t="s">
+        <v>87</v>
+      </c>
+      <c r="E2" s="1">
+        <v>10000</v>
+      </c>
+      <c r="F2" s="1">
+        <v>20000</v>
+      </c>
+      <c r="G2" s="1">
+        <v>5000</v>
+      </c>
+      <c r="H2" s="1">
+        <v>15000</v>
+      </c>
+      <c r="I2" s="1">
+        <v>25000</v>
+      </c>
+      <c r="J2" s="1" t="s">
+        <v>181</v>
+      </c>
+    </row>
+    <row r="3" spans="1:10" x14ac:dyDescent="0.3">
+      <c r="A3" s="1" t="s">
+        <v>182</v>
+      </c>
+      <c r="B3" s="1" t="s">
+        <v>183</v>
+      </c>
+      <c r="C3" s="1" t="s">
+        <v>105</v>
+      </c>
+      <c r="D3" s="1" t="s">
+        <v>104</v>
+      </c>
+      <c r="E3" s="1">
+        <v>10000</v>
+      </c>
+      <c r="F3" s="1">
+        <v>4500</v>
+      </c>
+      <c r="G3" s="1">
+        <v>4500</v>
+      </c>
+      <c r="H3" s="1">
+        <v>0</v>
+      </c>
+      <c r="I3" s="1">
+        <v>10000</v>
+      </c>
+      <c r="J3" s="1" t="s">
+        <v>184</v>
+      </c>
+    </row>
+  </sheetData>
+  <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
+  <tableParts count="1">
+    <tablePart r:id="rId1"/>
+  </tableParts>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet7.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{533C41CD-E6B4-46B6-AA50-9544EB3BB9D6}">
+  <dimension ref="A1:I3"/>
+  <sheetFormatPr baseColWidth="10" defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
+  <cols>
+    <col min="1" max="1" width="40" customWidth="1"/>
+    <col min="2" max="2" width="23" customWidth="1"/>
+    <col min="4" max="4" width="19.5546875" customWidth="1"/>
+    <col min="5" max="5" width="21.33203125" customWidth="1"/>
+    <col min="6" max="6" width="22.109375" customWidth="1"/>
+    <col min="8" max="8" width="17.6640625" customWidth="1"/>
+    <col min="9" max="9" width="19.88671875" customWidth="1"/>
+  </cols>
+  <sheetData>
+    <row r="1" spans="1:9" x14ac:dyDescent="0.3">
+      <c r="A1" s="1" t="s">
+        <v>185</v>
+      </c>
+      <c r="B1" s="1" t="s">
+        <v>1</v>
+      </c>
+      <c r="C1" s="1" t="s">
+        <v>80</v>
+      </c>
+      <c r="D1" s="1" t="s">
+        <v>173</v>
+      </c>
+      <c r="E1" s="1" t="s">
+        <v>174</v>
+      </c>
+      <c r="F1" s="1" t="s">
+        <v>175</v>
+      </c>
+      <c r="G1" s="1" t="s">
+        <v>176</v>
+      </c>
+      <c r="H1" s="1" t="s">
+        <v>177</v>
+      </c>
+      <c r="I1" s="1" t="s">
+        <v>178</v>
+      </c>
+    </row>
+    <row r="2" spans="1:9" x14ac:dyDescent="0.3">
+      <c r="A2" s="1" t="s">
+        <v>186</v>
+      </c>
+      <c r="B2" s="1" t="s">
+        <v>187</v>
+      </c>
+      <c r="C2" s="1" t="s">
+        <v>95</v>
+      </c>
+      <c r="D2" s="1">
+        <v>10000</v>
+      </c>
+      <c r="E2" s="1">
+        <v>68500</v>
+      </c>
+      <c r="F2" s="1">
+        <v>53000</v>
+      </c>
+      <c r="G2" s="1">
+        <v>15500</v>
+      </c>
+      <c r="H2" s="1">
+        <v>25500</v>
+      </c>
+      <c r="I2" s="1" t="s">
+        <v>181</v>
+      </c>
+    </row>
+    <row r="3" spans="1:9" x14ac:dyDescent="0.3">
+      <c r="A3" s="1" t="s">
+        <v>188</v>
+      </c>
+      <c r="B3" s="1" t="s">
+        <v>189</v>
+      </c>
+      <c r="C3" s="1" t="s">
+        <v>190</v>
+      </c>
+      <c r="D3" s="1">
+        <v>20000</v>
+      </c>
+      <c r="E3" s="1">
+        <v>10000</v>
+      </c>
+      <c r="F3" s="1">
+        <v>5000</v>
+      </c>
+      <c r="G3" s="1">
+        <v>5000</v>
+      </c>
+      <c r="H3" s="1">
+        <v>25000</v>
+      </c>
+      <c r="I3" s="1" t="s">
+        <v>191</v>
+      </c>
+    </row>
+  </sheetData>
+  <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
+  <tableParts count="1">
+    <tablePart r:id="rId1"/>
+  </tableParts>
 </worksheet>
 </file>